--- a/input/images/tables/uscdi-table.xlsx
+++ b/input/images/tables/uscdi-table.xlsx
@@ -523,7 +523,7 @@
       </c>
       <c r="D3" t="inlineStr">
         <is>
-          <t>Substance (Medication)</t>
+          <t>Medication Allergy Intolerance</t>
         </is>
       </c>
       <c r="E3" t="inlineStr">
@@ -563,7 +563,7 @@
       </c>
       <c r="D4" t="inlineStr">
         <is>
-          <t>Substance (Drug Class)</t>
+          <t>Drug Class Allergy Intolerance</t>
         </is>
       </c>
       <c r="E4" t="inlineStr">
@@ -603,7 +603,7 @@
       </c>
       <c r="D5" t="inlineStr">
         <is>
-          <t>Substance (Non-Medication)</t>
+          <t>Non-Medication Allergy Intolerance</t>
         </is>
       </c>
       <c r="E5" t="inlineStr">
@@ -670,30 +670,32 @@
       <c r="R6" t="inlineStr"/>
     </row>
     <row r="7">
-      <c r="A7" t="n">
-        <v>2</v>
-      </c>
+      <c r="A7" t="inlineStr"/>
       <c r="B7" t="inlineStr">
         <is>
-          <t>Care Plan</t>
+          <t>Allergies and Intolerances</t>
         </is>
       </c>
       <c r="C7" t="inlineStr">
         <is>
-          <t>US Core CarePlan Profile</t>
-        </is>
-      </c>
-      <c r="D7" t="inlineStr"/>
+          <t>US Core AllergyIntolerance Profile</t>
+        </is>
+      </c>
+      <c r="D7" t="inlineStr">
+        <is>
+          <t>Allergy Intolerance Criticality</t>
+        </is>
+      </c>
       <c r="E7" t="inlineStr">
         <is>
-          <t>CarePlan</t>
+          <t>AllergyIntolerance</t>
         </is>
       </c>
       <c r="F7" t="inlineStr"/>
       <c r="G7" t="inlineStr"/>
       <c r="H7" t="inlineStr">
         <is>
-          <t>CarePlan</t>
+          <t>AllergyIntolerance.criticality</t>
         </is>
       </c>
       <c r="I7" t="inlineStr"/>
@@ -708,10 +710,12 @@
       <c r="R7" t="inlineStr"/>
     </row>
     <row r="8">
-      <c r="A8" t="inlineStr"/>
+      <c r="A8" t="n">
+        <v>2</v>
+      </c>
       <c r="B8" t="inlineStr">
         <is>
-          <t>Care Plan</t>
+          <t>Care Plans</t>
         </is>
       </c>
       <c r="C8" t="inlineStr">
@@ -719,11 +723,7 @@
           <t>US Core CarePlan Profile</t>
         </is>
       </c>
-      <c r="D8" t="inlineStr">
-        <is>
-          <t>Care Plan</t>
-        </is>
-      </c>
+      <c r="D8" t="inlineStr"/>
       <c r="E8" t="inlineStr">
         <is>
           <t>CarePlan</t>
@@ -751,17 +751,17 @@
       <c r="A9" t="inlineStr"/>
       <c r="B9" t="inlineStr">
         <is>
+          <t>Care Plans</t>
+        </is>
+      </c>
+      <c r="C9" t="inlineStr">
+        <is>
+          <t>US Core CarePlan Profile</t>
+        </is>
+      </c>
+      <c r="D9" t="inlineStr">
+        <is>
           <t>Care Plan</t>
-        </is>
-      </c>
-      <c r="C9" t="inlineStr">
-        <is>
-          <t>US Core CarePlan Profile</t>
-        </is>
-      </c>
-      <c r="D9" t="inlineStr">
-        <is>
-          <t>Assessment and Plan of Treatment</t>
         </is>
       </c>
       <c r="E9" t="inlineStr">
@@ -788,26 +788,32 @@
       <c r="R9" t="inlineStr"/>
     </row>
     <row r="10">
-      <c r="A10" t="n">
-        <v>3</v>
-      </c>
+      <c r="A10" t="inlineStr"/>
       <c r="B10" t="inlineStr">
         <is>
-          <t>Care Team Members</t>
+          <t>Care Plans</t>
         </is>
       </c>
       <c r="C10" t="inlineStr">
         <is>
-          <t>US Core CareTeam Profile</t>
-        </is>
-      </c>
-      <c r="D10" t="inlineStr"/>
-      <c r="E10" t="inlineStr"/>
+          <t>US Core CarePlan Profile</t>
+        </is>
+      </c>
+      <c r="D10" t="inlineStr">
+        <is>
+          <t>Assessment and Plan of Treatment</t>
+        </is>
+      </c>
+      <c r="E10" t="inlineStr">
+        <is>
+          <t>CarePlan</t>
+        </is>
+      </c>
       <c r="F10" t="inlineStr"/>
       <c r="G10" t="inlineStr"/>
       <c r="H10" t="inlineStr">
         <is>
-          <t>CareTeam.participant</t>
+          <t>CarePlan</t>
         </is>
       </c>
       <c r="I10" t="inlineStr"/>
@@ -822,7 +828,9 @@
       <c r="R10" t="inlineStr"/>
     </row>
     <row r="11">
-      <c r="A11" t="inlineStr"/>
+      <c r="A11" t="n">
+        <v>3</v>
+      </c>
       <c r="B11" t="inlineStr">
         <is>
           <t>Care Team Members</t>
@@ -830,24 +838,16 @@
       </c>
       <c r="C11" t="inlineStr">
         <is>
-          <t>US Core Practitioner Profile| US Core Patient Profile| US Core RelatedPerson Profile</t>
-        </is>
-      </c>
-      <c r="D11" t="inlineStr">
-        <is>
-          <t>Name</t>
-        </is>
-      </c>
-      <c r="E11" t="inlineStr">
-        <is>
-          <t>CareTeam</t>
-        </is>
-      </c>
+          <t>US Core CareTeam Profile</t>
+        </is>
+      </c>
+      <c r="D11" t="inlineStr"/>
+      <c r="E11" t="inlineStr"/>
       <c r="F11" t="inlineStr"/>
       <c r="G11" t="inlineStr"/>
       <c r="H11" t="inlineStr">
         <is>
-          <t>Practitioner.name | RelatedPerson.name</t>
+          <t>CareTeam.participant</t>
         </is>
       </c>
       <c r="I11" t="inlineStr"/>
@@ -870,12 +870,12 @@
       </c>
       <c r="C12" t="inlineStr">
         <is>
-          <t>US Core Practitioner Profile| US Core Patient Profile</t>
+          <t>US Core Practitioner Profile| US Core Patient Profile| US Core RelatedPerson Profile</t>
         </is>
       </c>
       <c r="D12" t="inlineStr">
         <is>
-          <t>Identifier</t>
+          <t>Care Team Member Name</t>
         </is>
       </c>
       <c r="E12" t="inlineStr">
@@ -887,7 +887,7 @@
       <c r="G12" t="inlineStr"/>
       <c r="H12" t="inlineStr">
         <is>
-          <t>Practitioner.identifier</t>
+          <t>Practitioner.name | RelatedPerson.name</t>
         </is>
       </c>
       <c r="I12" t="inlineStr"/>
@@ -910,12 +910,12 @@
       </c>
       <c r="C13" t="inlineStr">
         <is>
-          <t>US Core PractitionerRole Profile| US Core Practitioner Profile| US Core Patient Profile| US Core RelatedPerson Profile</t>
+          <t>US Core Practitioner Profile| US Core Patient Profile</t>
         </is>
       </c>
       <c r="D13" t="inlineStr">
         <is>
-          <t>Location</t>
+          <t>Care Team Member Identifier</t>
         </is>
       </c>
       <c r="E13" t="inlineStr">
@@ -927,7 +927,7 @@
       <c r="G13" t="inlineStr"/>
       <c r="H13" t="inlineStr">
         <is>
-          <t>PractitionerRole.address | Practitioner.address | RelatedPerson.address</t>
+          <t>Practitioner.identifier</t>
         </is>
       </c>
       <c r="I13" t="inlineStr"/>
@@ -955,7 +955,7 @@
       </c>
       <c r="D14" t="inlineStr">
         <is>
-          <t>Telecom</t>
+          <t>Care Team Member Location</t>
         </is>
       </c>
       <c r="E14" t="inlineStr">
@@ -967,7 +967,7 @@
       <c r="G14" t="inlineStr"/>
       <c r="H14" t="inlineStr">
         <is>
-          <t>PractitionerRole.telecom | Practitioner.telecom | RelatedPerson.telecom</t>
+          <t>PractitionerRole.address | Practitioner.address | RelatedPerson.address</t>
         </is>
       </c>
       <c r="I14" t="inlineStr"/>
@@ -990,12 +990,12 @@
       </c>
       <c r="C15" t="inlineStr">
         <is>
-          <t>US Core CareTeam Profile</t>
+          <t>US Core PractitionerRole Profile| US Core Practitioner Profile| US Core Patient Profile| US Core RelatedPerson Profile</t>
         </is>
       </c>
       <c r="D15" t="inlineStr">
         <is>
-          <t>Role</t>
+          <t>Care Team Member Telecom</t>
         </is>
       </c>
       <c r="E15" t="inlineStr">
@@ -1007,7 +1007,7 @@
       <c r="G15" t="inlineStr"/>
       <c r="H15" t="inlineStr">
         <is>
-          <t>CareTeam.participant.role</t>
+          <t>PractitionerRole.telecom | Practitioner.telecom | RelatedPerson.telecom</t>
         </is>
       </c>
       <c r="I15" t="inlineStr"/>
@@ -1022,38 +1022,36 @@
       <c r="R15" t="inlineStr"/>
     </row>
     <row r="16">
-      <c r="A16" t="n">
-        <v>4</v>
-      </c>
+      <c r="A16" t="inlineStr"/>
       <c r="B16" t="inlineStr">
         <is>
-          <t>Clinical Notes</t>
+          <t>Care Team Members</t>
         </is>
       </c>
       <c r="C16" t="inlineStr">
         <is>
-          <t>US Core DocumentReference Profile|US Core DiagnosticReport Profile for Report and Note Exchange</t>
-        </is>
-      </c>
-      <c r="D16" t="inlineStr"/>
-      <c r="E16" t="inlineStr"/>
+          <t>US Core CareTeam Profile</t>
+        </is>
+      </c>
+      <c r="D16" t="inlineStr">
+        <is>
+          <t>Care Team Member Role</t>
+        </is>
+      </c>
+      <c r="E16" t="inlineStr">
+        <is>
+          <t>CareTeam</t>
+        </is>
+      </c>
       <c r="F16" t="inlineStr"/>
       <c r="G16" t="inlineStr"/>
       <c r="H16" t="inlineStr">
         <is>
-          <t>DocumentReference | DiagnosticReport</t>
-        </is>
-      </c>
-      <c r="I16" t="inlineStr">
-        <is>
-          <t>See Clinical Notes Guidance</t>
-        </is>
-      </c>
-      <c r="J16" t="inlineStr">
-        <is>
-          <t>clinical-notes.html</t>
-        </is>
-      </c>
+          <t>CareTeam.participant.role</t>
+        </is>
+      </c>
+      <c r="I16" t="inlineStr"/>
+      <c r="J16" t="inlineStr"/>
       <c r="K16" t="inlineStr"/>
       <c r="L16" t="inlineStr"/>
       <c r="M16" t="inlineStr"/>
@@ -1067,29 +1065,29 @@
       <c r="A17" t="inlineStr"/>
       <c r="B17" t="inlineStr">
         <is>
-          <t>Clinical Notes</t>
+          <t>Care Team Members</t>
         </is>
       </c>
       <c r="C17" t="inlineStr">
         <is>
-          <t>US Core DocumentReference Profile</t>
+          <t>US Core CareTeam Profile| US Core RelatedPerson Profile</t>
         </is>
       </c>
       <c r="D17" t="inlineStr">
         <is>
-          <t>Consultation Note</t>
+          <t>Healthcare Agent</t>
         </is>
       </c>
       <c r="E17" t="inlineStr">
         <is>
-          <t>DocumentReference</t>
+          <t>CareTeam | RelatedPerson</t>
         </is>
       </c>
       <c r="F17" t="inlineStr"/>
       <c r="G17" t="inlineStr"/>
       <c r="H17" t="inlineStr">
         <is>
-          <t>DocumentReference</t>
+          <t>CareTeam.participant.role | RelatedPerson.relationship</t>
         </is>
       </c>
       <c r="I17" t="inlineStr"/>
@@ -1104,7 +1102,9 @@
       <c r="R17" t="inlineStr"/>
     </row>
     <row r="18">
-      <c r="A18" t="inlineStr"/>
+      <c r="A18" t="n">
+        <v>4</v>
+      </c>
       <c r="B18" t="inlineStr">
         <is>
           <t>Clinical Notes</t>
@@ -1112,28 +1112,28 @@
       </c>
       <c r="C18" t="inlineStr">
         <is>
-          <t>US Core DocumentReference Profile</t>
-        </is>
-      </c>
-      <c r="D18" t="inlineStr">
-        <is>
-          <t>Discharge Summary Note</t>
-        </is>
-      </c>
-      <c r="E18" t="inlineStr">
-        <is>
-          <t>DocumentReference</t>
-        </is>
-      </c>
+          <t>US Core DocumentReference Profile|US Core DiagnosticReport Profile for Report and Note Exchange</t>
+        </is>
+      </c>
+      <c r="D18" t="inlineStr"/>
+      <c r="E18" t="inlineStr"/>
       <c r="F18" t="inlineStr"/>
       <c r="G18" t="inlineStr"/>
       <c r="H18" t="inlineStr">
         <is>
-          <t>DocumentReference</t>
-        </is>
-      </c>
-      <c r="I18" t="inlineStr"/>
-      <c r="J18" t="inlineStr"/>
+          <t>DocumentReference | DiagnosticReport</t>
+        </is>
+      </c>
+      <c r="I18" t="inlineStr">
+        <is>
+          <t>See Clinical Notes Guidance</t>
+        </is>
+      </c>
+      <c r="J18" t="inlineStr">
+        <is>
+          <t>clinical-notes.html</t>
+        </is>
+      </c>
       <c r="K18" t="inlineStr"/>
       <c r="L18" t="inlineStr"/>
       <c r="M18" t="inlineStr"/>
@@ -1157,7 +1157,7 @@
       </c>
       <c r="D19" t="inlineStr">
         <is>
-          <t>History &amp; Physical</t>
+          <t>Consultation Note</t>
         </is>
       </c>
       <c r="E19" t="inlineStr">
@@ -1192,24 +1192,24 @@
       </c>
       <c r="C20" t="inlineStr">
         <is>
-          <t>US Core DocumentReference Profile|US Core DiagnosticReport Profile for Report and Note Exchange</t>
+          <t>US Core DocumentReference Profile</t>
         </is>
       </c>
       <c r="D20" t="inlineStr">
         <is>
-          <t>Imaging Narrative</t>
+          <t>Discharge Summary Note</t>
         </is>
       </c>
       <c r="E20" t="inlineStr">
         <is>
-          <t>DocumentReference | DiagnosticReport</t>
+          <t>DocumentReference</t>
         </is>
       </c>
       <c r="F20" t="inlineStr"/>
       <c r="G20" t="inlineStr"/>
       <c r="H20" t="inlineStr">
         <is>
-          <t>DocumentReference | DiagnosticReport</t>
+          <t>DocumentReference</t>
         </is>
       </c>
       <c r="I20" t="inlineStr"/>
@@ -1232,24 +1232,24 @@
       </c>
       <c r="C21" t="inlineStr">
         <is>
-          <t>US Core DocumentReference Profile|US Core DiagnosticReport Profile for Report and Note Exchange</t>
+          <t>US Core DocumentReference Profile</t>
         </is>
       </c>
       <c r="D21" t="inlineStr">
         <is>
-          <t>Procedure Note</t>
+          <t>History &amp; Physical</t>
         </is>
       </c>
       <c r="E21" t="inlineStr">
         <is>
-          <t>DocumentReference | DiagnosticReport</t>
+          <t>DocumentReference</t>
         </is>
       </c>
       <c r="F21" t="inlineStr"/>
       <c r="G21" t="inlineStr"/>
       <c r="H21" t="inlineStr">
         <is>
-          <t>DocumentReference | DiagnosticReport</t>
+          <t>DocumentReference</t>
         </is>
       </c>
       <c r="I21" t="inlineStr"/>
@@ -1272,20 +1272,24 @@
       </c>
       <c r="C22" t="inlineStr">
         <is>
-          <t>US Core DocumentReference Profile</t>
+          <t>US Core DocumentReference Profile|US Core DiagnosticReport Profile for Report and Note Exchange</t>
         </is>
       </c>
       <c r="D22" t="inlineStr">
         <is>
-          <t>Progress Note</t>
-        </is>
-      </c>
-      <c r="E22" t="inlineStr"/>
+          <t>Procedure Note</t>
+        </is>
+      </c>
+      <c r="E22" t="inlineStr">
+        <is>
+          <t>DocumentReference | DiagnosticReport</t>
+        </is>
+      </c>
       <c r="F22" t="inlineStr"/>
       <c r="G22" t="inlineStr"/>
       <c r="H22" t="inlineStr">
         <is>
-          <t>DocumentReference</t>
+          <t>DocumentReference | DiagnosticReport</t>
         </is>
       </c>
       <c r="I22" t="inlineStr"/>
@@ -1313,7 +1317,7 @@
       </c>
       <c r="D23" t="inlineStr">
         <is>
-          <t>Operative Note</t>
+          <t>Progress Note</t>
         </is>
       </c>
       <c r="E23" t="inlineStr"/>
@@ -1349,7 +1353,7 @@
       </c>
       <c r="D24" t="inlineStr">
         <is>
-          <t>Emergency Department Note</t>
+          <t>Operative Note</t>
         </is>
       </c>
       <c r="E24" t="inlineStr"/>
@@ -1372,34 +1376,28 @@
       <c r="R24" t="inlineStr"/>
     </row>
     <row r="25">
-      <c r="A25" t="n">
-        <v>5</v>
-      </c>
+      <c r="A25" t="inlineStr"/>
       <c r="B25" t="inlineStr">
         <is>
-          <t>Clinical Tests</t>
+          <t>Clinical Notes</t>
         </is>
       </c>
       <c r="C25" t="inlineStr">
         <is>
-          <t>US Core Observation Clinical Result Profile| US Core DiagnosticReport Profile for Report and Note Exchange</t>
+          <t>US Core DocumentReference Profile</t>
         </is>
       </c>
       <c r="D25" t="inlineStr">
         <is>
-          <t>Clinical Tests</t>
-        </is>
-      </c>
-      <c r="E25" t="inlineStr">
-        <is>
-          <t>Observation | DiagnosticReport</t>
-        </is>
-      </c>
+          <t>Emergency Department Note</t>
+        </is>
+      </c>
+      <c r="E25" t="inlineStr"/>
       <c r="F25" t="inlineStr"/>
       <c r="G25" t="inlineStr"/>
       <c r="H25" t="inlineStr">
         <is>
-          <t>Observation | DiagnosticReport</t>
+          <t>DocumentReference</t>
         </is>
       </c>
       <c r="I25" t="inlineStr"/>
@@ -1417,29 +1415,29 @@
       <c r="A26" t="inlineStr"/>
       <c r="B26" t="inlineStr">
         <is>
-          <t>Clinical Tests</t>
+          <t>Clinical Notes</t>
         </is>
       </c>
       <c r="C26" t="inlineStr">
         <is>
-          <t>US Core Observation Clinical Result Profile| US Core DiagnosticReport Profile for Report and Note Exchange</t>
+          <t>US Core DocumentReference Profile</t>
         </is>
       </c>
       <c r="D26" t="inlineStr">
         <is>
-          <t>Clinical Test</t>
+          <t>Referral Note</t>
         </is>
       </c>
       <c r="E26" t="inlineStr">
         <is>
-          <t>Observation | DiagnosticReport</t>
+          <t>DocumentReference</t>
         </is>
       </c>
       <c r="F26" t="inlineStr"/>
       <c r="G26" t="inlineStr"/>
       <c r="H26" t="inlineStr">
         <is>
-          <t>Observation | DiagnosticReport</t>
+          <t>DocumentReference</t>
         </is>
       </c>
       <c r="I26" t="inlineStr"/>
@@ -1454,7 +1452,9 @@
       <c r="R26" t="inlineStr"/>
     </row>
     <row r="27">
-      <c r="A27" t="inlineStr"/>
+      <c r="A27" t="n">
+        <v>5</v>
+      </c>
       <c r="B27" t="inlineStr">
         <is>
           <t>Clinical Tests</t>
@@ -1465,11 +1465,7 @@
           <t>US Core Observation Clinical Result Profile| US Core DiagnosticReport Profile for Report and Note Exchange</t>
         </is>
       </c>
-      <c r="D27" t="inlineStr">
-        <is>
-          <t>Clinical Test Result/Report</t>
-        </is>
-      </c>
+      <c r="D27" t="inlineStr"/>
       <c r="E27" t="inlineStr">
         <is>
           <t>Observation | DiagnosticReport</t>
@@ -1494,12 +1490,10 @@
       <c r="R27" t="inlineStr"/>
     </row>
     <row r="28">
-      <c r="A28" t="n">
-        <v>6</v>
-      </c>
+      <c r="A28" t="inlineStr"/>
       <c r="B28" t="inlineStr">
         <is>
-          <t>Diagnostic Imaging</t>
+          <t>Clinical Tests</t>
         </is>
       </c>
       <c r="C28" t="inlineStr">
@@ -1507,8 +1501,16 @@
           <t>US Core Observation Clinical Result Profile| US Core DiagnosticReport Profile for Report and Note Exchange</t>
         </is>
       </c>
-      <c r="D28" t="inlineStr"/>
-      <c r="E28" t="inlineStr"/>
+      <c r="D28" t="inlineStr">
+        <is>
+          <t>Clinical Test</t>
+        </is>
+      </c>
+      <c r="E28" t="inlineStr">
+        <is>
+          <t>Observation | DiagnosticReport</t>
+        </is>
+      </c>
       <c r="F28" t="inlineStr"/>
       <c r="G28" t="inlineStr"/>
       <c r="H28" t="inlineStr">
@@ -1531,7 +1533,7 @@
       <c r="A29" t="inlineStr"/>
       <c r="B29" t="inlineStr">
         <is>
-          <t>Diagnostic Imaging</t>
+          <t>Clinical Tests</t>
         </is>
       </c>
       <c r="C29" t="inlineStr">
@@ -1541,7 +1543,7 @@
       </c>
       <c r="D29" t="inlineStr">
         <is>
-          <t>Diagnostic Imaging Test</t>
+          <t>Clinical Test Result/Report</t>
         </is>
       </c>
       <c r="E29" t="inlineStr">
@@ -1568,7 +1570,9 @@
       <c r="R29" t="inlineStr"/>
     </row>
     <row r="30">
-      <c r="A30" t="inlineStr"/>
+      <c r="A30" t="n">
+        <v>6</v>
+      </c>
       <c r="B30" t="inlineStr">
         <is>
           <t>Diagnostic Imaging</t>
@@ -1579,16 +1583,8 @@
           <t>US Core Observation Clinical Result Profile| US Core DiagnosticReport Profile for Report and Note Exchange</t>
         </is>
       </c>
-      <c r="D30" t="inlineStr">
-        <is>
-          <t>Diagnostic Imaging Result/Report</t>
-        </is>
-      </c>
-      <c r="E30" t="inlineStr">
-        <is>
-          <t>Observation | DiagnosticReport</t>
-        </is>
-      </c>
+      <c r="D30" t="inlineStr"/>
+      <c r="E30" t="inlineStr"/>
       <c r="F30" t="inlineStr"/>
       <c r="G30" t="inlineStr"/>
       <c r="H30" t="inlineStr">
@@ -1608,26 +1604,32 @@
       <c r="R30" t="inlineStr"/>
     </row>
     <row r="31">
-      <c r="A31" t="n">
-        <v>7</v>
-      </c>
+      <c r="A31" t="inlineStr"/>
       <c r="B31" t="inlineStr">
         <is>
-          <t>Encounter</t>
+          <t>Diagnostic Imaging</t>
         </is>
       </c>
       <c r="C31" t="inlineStr">
         <is>
-          <t>US Core Encounter Profile</t>
-        </is>
-      </c>
-      <c r="D31" t="inlineStr"/>
-      <c r="E31" t="inlineStr"/>
+          <t>US Core Observation Clinical Result Profile| US Core DiagnosticReport Profile for Report and Note Exchange</t>
+        </is>
+      </c>
+      <c r="D31" t="inlineStr">
+        <is>
+          <t>Diagnostic Imaging Test</t>
+        </is>
+      </c>
+      <c r="E31" t="inlineStr">
+        <is>
+          <t>Observation | DiagnosticReport</t>
+        </is>
+      </c>
       <c r="F31" t="inlineStr"/>
       <c r="G31" t="inlineStr"/>
       <c r="H31" t="inlineStr">
         <is>
-          <t>Encounter</t>
+          <t>Observation | DiagnosticReport</t>
         </is>
       </c>
       <c r="I31" t="inlineStr"/>
@@ -1645,29 +1647,29 @@
       <c r="A32" t="inlineStr"/>
       <c r="B32" t="inlineStr">
         <is>
-          <t>Encounter</t>
+          <t>Diagnostic Imaging</t>
         </is>
       </c>
       <c r="C32" t="inlineStr">
         <is>
-          <t>US Core Encounter Profile</t>
+          <t>US Core Observation Clinical Result Profile| US Core DiagnosticReport Profile for Report and Note Exchange</t>
         </is>
       </c>
       <c r="D32" t="inlineStr">
         <is>
-          <t>Identifier</t>
+          <t>Diagnostic Imaging Result/Report</t>
         </is>
       </c>
       <c r="E32" t="inlineStr">
         <is>
-          <t>Encounter</t>
+          <t>Observation | DiagnosticReport</t>
         </is>
       </c>
       <c r="F32" t="inlineStr"/>
       <c r="G32" t="inlineStr"/>
       <c r="H32" t="inlineStr">
         <is>
-          <t>Encounter.identifier</t>
+          <t>Observation | DiagnosticReport</t>
         </is>
       </c>
       <c r="I32" t="inlineStr"/>
@@ -1682,10 +1684,12 @@
       <c r="R32" t="inlineStr"/>
     </row>
     <row r="33">
-      <c r="A33" t="inlineStr"/>
+      <c r="A33" t="n">
+        <v>7</v>
+      </c>
       <c r="B33" t="inlineStr">
         <is>
-          <t>Encounter</t>
+          <t>Encounter Information</t>
         </is>
       </c>
       <c r="C33" t="inlineStr">
@@ -1693,21 +1697,13 @@
           <t>US Core Encounter Profile</t>
         </is>
       </c>
-      <c r="D33" t="inlineStr">
-        <is>
-          <t>Type</t>
-        </is>
-      </c>
-      <c r="E33" t="inlineStr">
-        <is>
-          <t>Encounter</t>
-        </is>
-      </c>
+      <c r="D33" t="inlineStr"/>
+      <c r="E33" t="inlineStr"/>
       <c r="F33" t="inlineStr"/>
       <c r="G33" t="inlineStr"/>
       <c r="H33" t="inlineStr">
         <is>
-          <t>Encounter.type</t>
+          <t>Encounter</t>
         </is>
       </c>
       <c r="I33" t="inlineStr"/>
@@ -1725,29 +1721,29 @@
       <c r="A34" t="inlineStr"/>
       <c r="B34" t="inlineStr">
         <is>
+          <t>Encounter Information</t>
+        </is>
+      </c>
+      <c r="C34" t="inlineStr">
+        <is>
+          <t>US Core Encounter Profile</t>
+        </is>
+      </c>
+      <c r="D34" t="inlineStr">
+        <is>
+          <t>Encounter Identifier</t>
+        </is>
+      </c>
+      <c r="E34" t="inlineStr">
+        <is>
           <t>Encounter</t>
-        </is>
-      </c>
-      <c r="C34" t="inlineStr">
-        <is>
-          <t>US Core Condition Encounter Diagnosis Profile</t>
-        </is>
-      </c>
-      <c r="D34" t="inlineStr">
-        <is>
-          <t>Diagnosis</t>
-        </is>
-      </c>
-      <c r="E34" t="inlineStr">
-        <is>
-          <t>Condition</t>
         </is>
       </c>
       <c r="F34" t="inlineStr"/>
       <c r="G34" t="inlineStr"/>
       <c r="H34" t="inlineStr">
         <is>
-          <t>Condition.code</t>
+          <t>Encounter.identifier</t>
         </is>
       </c>
       <c r="I34" t="inlineStr"/>
@@ -1765,7 +1761,7 @@
       <c r="A35" t="inlineStr"/>
       <c r="B35" t="inlineStr">
         <is>
-          <t>Encounter</t>
+          <t>Encounter Information</t>
         </is>
       </c>
       <c r="C35" t="inlineStr">
@@ -1775,7 +1771,7 @@
       </c>
       <c r="D35" t="inlineStr">
         <is>
-          <t>Time</t>
+          <t>Encounter Type</t>
         </is>
       </c>
       <c r="E35" t="inlineStr">
@@ -1787,7 +1783,7 @@
       <c r="G35" t="inlineStr"/>
       <c r="H35" t="inlineStr">
         <is>
-          <t>Encounter.period</t>
+          <t>Encounter.type</t>
         </is>
       </c>
       <c r="I35" t="inlineStr"/>
@@ -1805,29 +1801,29 @@
       <c r="A36" t="inlineStr"/>
       <c r="B36" t="inlineStr">
         <is>
-          <t>Encounter</t>
+          <t>Encounter Information</t>
         </is>
       </c>
       <c r="C36" t="inlineStr">
         <is>
-          <t>US Core Encounter Profile</t>
+          <t>US Core Condition Encounter Diagnosis Profile</t>
         </is>
       </c>
       <c r="D36" t="inlineStr">
         <is>
-          <t>Location</t>
+          <t>Encounter Diagnosis</t>
         </is>
       </c>
       <c r="E36" t="inlineStr">
         <is>
-          <t>Encounter</t>
+          <t>Condition</t>
         </is>
       </c>
       <c r="F36" t="inlineStr"/>
       <c r="G36" t="inlineStr"/>
       <c r="H36" t="inlineStr">
         <is>
-          <t>Encounter.location.location</t>
+          <t>Condition.code</t>
         </is>
       </c>
       <c r="I36" t="inlineStr"/>
@@ -1845,7 +1841,7 @@
       <c r="A37" t="inlineStr"/>
       <c r="B37" t="inlineStr">
         <is>
-          <t>Encounter</t>
+          <t>Encounter Information</t>
         </is>
       </c>
       <c r="C37" t="inlineStr">
@@ -1855,7 +1851,7 @@
       </c>
       <c r="D37" t="inlineStr">
         <is>
-          <t>Disposition</t>
+          <t>Encounter Date and Time</t>
         </is>
       </c>
       <c r="E37" t="inlineStr">
@@ -1867,7 +1863,7 @@
       <c r="G37" t="inlineStr"/>
       <c r="H37" t="inlineStr">
         <is>
-          <t>Encounter.hospitalization.dischargeDisposition</t>
+          <t>Encounter.period</t>
         </is>
       </c>
       <c r="I37" t="inlineStr"/>
@@ -1882,38 +1878,36 @@
       <c r="R37" t="inlineStr"/>
     </row>
     <row r="38">
-      <c r="A38" t="n">
-        <v>8</v>
-      </c>
+      <c r="A38" t="inlineStr"/>
       <c r="B38" t="inlineStr">
         <is>
-          <t>Facility Information</t>
+          <t>Encounter Information</t>
         </is>
       </c>
       <c r="C38" t="inlineStr">
         <is>
-          <t>US Core Location Profile</t>
-        </is>
-      </c>
-      <c r="D38" t="inlineStr"/>
-      <c r="E38" t="inlineStr"/>
+          <t>US Core Encounter Profile</t>
+        </is>
+      </c>
+      <c r="D38" t="inlineStr">
+        <is>
+          <t>Encounter Location</t>
+        </is>
+      </c>
+      <c r="E38" t="inlineStr">
+        <is>
+          <t>Encounter</t>
+        </is>
+      </c>
       <c r="F38" t="inlineStr"/>
       <c r="G38" t="inlineStr"/>
       <c r="H38" t="inlineStr">
         <is>
-          <t>Location</t>
-        </is>
-      </c>
-      <c r="I38" t="inlineStr">
-        <is>
-          <t>See Facility Information Guidance</t>
-        </is>
-      </c>
-      <c r="J38" t="inlineStr">
-        <is>
-          <t>StructureDefinition-us-core-location.html</t>
-        </is>
-      </c>
+          <t>Encounter.location.location</t>
+        </is>
+      </c>
+      <c r="I38" t="inlineStr"/>
+      <c r="J38" t="inlineStr"/>
       <c r="K38" t="inlineStr"/>
       <c r="L38" t="inlineStr"/>
       <c r="M38" t="inlineStr"/>
@@ -1927,29 +1921,29 @@
       <c r="A39" t="inlineStr"/>
       <c r="B39" t="inlineStr">
         <is>
-          <t>Facility Information</t>
+          <t>Encounter Information</t>
         </is>
       </c>
       <c r="C39" t="inlineStr">
         <is>
-          <t>US Core Location Profile</t>
+          <t>US Core Encounter Profile</t>
         </is>
       </c>
       <c r="D39" t="inlineStr">
         <is>
-          <t>Identifier</t>
+          <t>Encounter Disposition</t>
         </is>
       </c>
       <c r="E39" t="inlineStr">
         <is>
-          <t>Location</t>
+          <t>Encounter</t>
         </is>
       </c>
       <c r="F39" t="inlineStr"/>
       <c r="G39" t="inlineStr"/>
       <c r="H39" t="inlineStr">
         <is>
-          <t>Location.identifier</t>
+          <t>Encounter.hospitalization.dischargeDisposition</t>
         </is>
       </c>
       <c r="I39" t="inlineStr"/>
@@ -1967,29 +1961,29 @@
       <c r="A40" t="inlineStr"/>
       <c r="B40" t="inlineStr">
         <is>
-          <t>Facility Information</t>
+          <t>Encounter Information</t>
         </is>
       </c>
       <c r="C40" t="inlineStr">
         <is>
-          <t>US Core Location Profile</t>
+          <t>US Core Appointment Profile</t>
         </is>
       </c>
       <c r="D40" t="inlineStr">
         <is>
-          <t>Type</t>
+          <t>Appointment</t>
         </is>
       </c>
       <c r="E40" t="inlineStr">
         <is>
-          <t>Location</t>
+          <t>Appointment</t>
         </is>
       </c>
       <c r="F40" t="inlineStr"/>
       <c r="G40" t="inlineStr"/>
       <c r="H40" t="inlineStr">
         <is>
-          <t>Location.type</t>
+          <t>Appointment</t>
         </is>
       </c>
       <c r="I40" t="inlineStr"/>
@@ -2004,7 +1998,9 @@
       <c r="R40" t="inlineStr"/>
     </row>
     <row r="41">
-      <c r="A41" t="inlineStr"/>
+      <c r="A41" t="n">
+        <v>8</v>
+      </c>
       <c r="B41" t="inlineStr">
         <is>
           <t>Facility Information</t>
@@ -2015,25 +2011,25 @@
           <t>US Core Location Profile</t>
         </is>
       </c>
-      <c r="D41" t="inlineStr">
-        <is>
-          <t>Name</t>
-        </is>
-      </c>
-      <c r="E41" t="inlineStr">
-        <is>
-          <t>Location</t>
-        </is>
-      </c>
+      <c r="D41" t="inlineStr"/>
+      <c r="E41" t="inlineStr"/>
       <c r="F41" t="inlineStr"/>
       <c r="G41" t="inlineStr"/>
       <c r="H41" t="inlineStr">
         <is>
-          <t>Location.name</t>
-        </is>
-      </c>
-      <c r="I41" t="inlineStr"/>
-      <c r="J41" t="inlineStr"/>
+          <t>Location</t>
+        </is>
+      </c>
+      <c r="I41" t="inlineStr">
+        <is>
+          <t>See Facility Information Guidance</t>
+        </is>
+      </c>
+      <c r="J41" t="inlineStr">
+        <is>
+          <t>StructureDefinition-us-core-location.html</t>
+        </is>
+      </c>
       <c r="K41" t="inlineStr"/>
       <c r="L41" t="inlineStr"/>
       <c r="M41" t="inlineStr"/>
@@ -2057,7 +2053,7 @@
       </c>
       <c r="D42" t="inlineStr">
         <is>
-          <t>Address</t>
+          <t>Facility Identifier</t>
         </is>
       </c>
       <c r="E42" t="inlineStr">
@@ -2069,7 +2065,7 @@
       <c r="G42" t="inlineStr"/>
       <c r="H42" t="inlineStr">
         <is>
-          <t>Location.adress</t>
+          <t>Location.identifier</t>
         </is>
       </c>
       <c r="I42" t="inlineStr"/>
@@ -2084,26 +2080,32 @@
       <c r="R42" t="inlineStr"/>
     </row>
     <row r="43">
-      <c r="A43" t="n">
-        <v>9</v>
-      </c>
+      <c r="A43" t="inlineStr"/>
       <c r="B43" t="inlineStr">
         <is>
-          <t>Family Health History</t>
+          <t>Facility Information</t>
         </is>
       </c>
       <c r="C43" t="inlineStr">
         <is>
-          <t>US Core FamilyMemberHistory Profile</t>
-        </is>
-      </c>
-      <c r="D43" t="inlineStr"/>
-      <c r="E43" t="inlineStr"/>
+          <t>US Core Location Profile</t>
+        </is>
+      </c>
+      <c r="D43" t="inlineStr">
+        <is>
+          <t>Facility Type</t>
+        </is>
+      </c>
+      <c r="E43" t="inlineStr">
+        <is>
+          <t>Location</t>
+        </is>
+      </c>
       <c r="F43" t="inlineStr"/>
       <c r="G43" t="inlineStr"/>
       <c r="H43" t="inlineStr">
         <is>
-          <t>FamilyMemberHistory</t>
+          <t>Location.type</t>
         </is>
       </c>
       <c r="I43" t="inlineStr"/>
@@ -2121,29 +2123,29 @@
       <c r="A44" t="inlineStr"/>
       <c r="B44" t="inlineStr">
         <is>
-          <t>Family Health History</t>
+          <t>Facility Information</t>
         </is>
       </c>
       <c r="C44" t="inlineStr">
         <is>
-          <t>US Core FamilyMemberHistory Profile</t>
+          <t>US Core Location Profile</t>
         </is>
       </c>
       <c r="D44" t="inlineStr">
         <is>
-          <t>Family Health History</t>
+          <t>Facility Name</t>
         </is>
       </c>
       <c r="E44" t="inlineStr">
         <is>
-          <t>FamilyMemberHistory</t>
+          <t>Location</t>
         </is>
       </c>
       <c r="F44" t="inlineStr"/>
       <c r="G44" t="inlineStr"/>
       <c r="H44" t="inlineStr">
         <is>
-          <t>FamilyMemberHistory</t>
+          <t>Location.name</t>
         </is>
       </c>
       <c r="I44" t="inlineStr"/>
@@ -2158,26 +2160,32 @@
       <c r="R44" t="inlineStr"/>
     </row>
     <row r="45">
-      <c r="A45" t="n">
-        <v>10</v>
-      </c>
+      <c r="A45" t="inlineStr"/>
       <c r="B45" t="inlineStr">
         <is>
-          <t>Goals and Preferences</t>
+          <t>Facility Information</t>
         </is>
       </c>
       <c r="C45" t="inlineStr">
         <is>
-          <t>US Core Goal Profile |  US Core Observation ADI Documentation Profile| US Core ADI DocumentReference Profile | US Core Treatment Intervention Preference Profile | US Core Care Experience Preference Profile</t>
-        </is>
-      </c>
-      <c r="D45" t="inlineStr"/>
-      <c r="E45" t="inlineStr"/>
+          <t>US Core Location Profile</t>
+        </is>
+      </c>
+      <c r="D45" t="inlineStr">
+        <is>
+          <t>Facility Address</t>
+        </is>
+      </c>
+      <c r="E45" t="inlineStr">
+        <is>
+          <t>Location</t>
+        </is>
+      </c>
       <c r="F45" t="inlineStr"/>
       <c r="G45" t="inlineStr"/>
       <c r="H45" t="inlineStr">
         <is>
-          <t>Goal</t>
+          <t>Location.adress</t>
         </is>
       </c>
       <c r="I45" t="inlineStr"/>
@@ -2195,29 +2203,29 @@
       <c r="A46" t="inlineStr"/>
       <c r="B46" t="inlineStr">
         <is>
-          <t>Goals and Preferences</t>
+          <t>Facility Information</t>
         </is>
       </c>
       <c r="C46" t="inlineStr">
         <is>
-          <t>US Core Goal Profile</t>
+          <t>US Core Location Profile</t>
         </is>
       </c>
       <c r="D46" t="inlineStr">
         <is>
-          <t>Patient Goals</t>
+          <t>Facility Telecom</t>
         </is>
       </c>
       <c r="E46" t="inlineStr">
         <is>
-          <t>Goal</t>
+          <t>Location</t>
         </is>
       </c>
       <c r="F46" t="inlineStr"/>
       <c r="G46" t="inlineStr"/>
       <c r="H46" t="inlineStr">
         <is>
-          <t>Goal</t>
+          <t>Location.telecom</t>
         </is>
       </c>
       <c r="I46" t="inlineStr"/>
@@ -2232,44 +2240,30 @@
       <c r="R46" t="inlineStr"/>
     </row>
     <row r="47">
-      <c r="A47" t="inlineStr"/>
+      <c r="A47" t="n">
+        <v>9</v>
+      </c>
       <c r="B47" t="inlineStr">
         <is>
-          <t>Goals and Preferences</t>
+          <t>Family Health History</t>
         </is>
       </c>
       <c r="C47" t="inlineStr">
         <is>
-          <t>US Core Goal Profile</t>
-        </is>
-      </c>
-      <c r="D47" t="inlineStr">
-        <is>
-          <t>SDOH Goals</t>
-        </is>
-      </c>
-      <c r="E47" t="inlineStr">
-        <is>
-          <t>Goal</t>
-        </is>
-      </c>
+          <t>US Core FamilyMemberHistory Profile</t>
+        </is>
+      </c>
+      <c r="D47" t="inlineStr"/>
+      <c r="E47" t="inlineStr"/>
       <c r="F47" t="inlineStr"/>
       <c r="G47" t="inlineStr"/>
       <c r="H47" t="inlineStr">
         <is>
-          <t>Goal</t>
-        </is>
-      </c>
-      <c r="I47" t="inlineStr">
-        <is>
-          <t>See Screening and Assessments Guidance</t>
-        </is>
-      </c>
-      <c r="J47" t="inlineStr">
-        <is>
-          <t>screening-and-assessments.html</t>
-        </is>
-      </c>
+          <t>FamilyMemberHistory</t>
+        </is>
+      </c>
+      <c r="I47" t="inlineStr"/>
+      <c r="J47" t="inlineStr"/>
       <c r="K47" t="inlineStr"/>
       <c r="L47" t="inlineStr"/>
       <c r="M47" t="inlineStr"/>
@@ -2283,29 +2277,29 @@
       <c r="A48" t="inlineStr"/>
       <c r="B48" t="inlineStr">
         <is>
-          <t>Goals and Preferences</t>
+          <t>Family Health History</t>
         </is>
       </c>
       <c r="C48" t="inlineStr">
         <is>
-          <t>US Core Observation ADI Documentation Profile| US Core ADI DocumentReference Profile</t>
+          <t>US Core FamilyMemberHistory Profile</t>
         </is>
       </c>
       <c r="D48" t="inlineStr">
         <is>
-          <t>Advance Directive Observation</t>
+          <t>Family Health History</t>
         </is>
       </c>
       <c r="E48" t="inlineStr">
         <is>
-          <t>Observation | DocumentReference</t>
+          <t>FamilyMemberHistory</t>
         </is>
       </c>
       <c r="F48" t="inlineStr"/>
       <c r="G48" t="inlineStr"/>
       <c r="H48" t="inlineStr">
         <is>
-          <t>Observation | DocumentReference</t>
+          <t>FamilyMemberHistory</t>
         </is>
       </c>
       <c r="I48" t="inlineStr"/>
@@ -2320,7 +2314,9 @@
       <c r="R48" t="inlineStr"/>
     </row>
     <row r="49">
-      <c r="A49" t="inlineStr"/>
+      <c r="A49" t="n">
+        <v>10</v>
+      </c>
       <c r="B49" t="inlineStr">
         <is>
           <t>Goals and Preferences</t>
@@ -2328,24 +2324,16 @@
       </c>
       <c r="C49" t="inlineStr">
         <is>
-          <t>US Core Treatment Intervention Preference Profile</t>
-        </is>
-      </c>
-      <c r="D49" t="inlineStr">
-        <is>
-          <t>Treatment Intervention Preference</t>
-        </is>
-      </c>
-      <c r="E49" t="inlineStr">
-        <is>
-          <t>Observation</t>
-        </is>
-      </c>
+          <t>US Core Goal Profile |  US Core Observation ADI Documentation Profile| US Core ADI DocumentReference Profile | US Core Treatment Intervention Preference Profile | US Core Care Experience Preference Profile</t>
+        </is>
+      </c>
+      <c r="D49" t="inlineStr"/>
+      <c r="E49" t="inlineStr"/>
       <c r="F49" t="inlineStr"/>
       <c r="G49" t="inlineStr"/>
       <c r="H49" t="inlineStr">
         <is>
-          <t>Observation</t>
+          <t>Goal</t>
         </is>
       </c>
       <c r="I49" t="inlineStr"/>
@@ -2368,28 +2356,36 @@
       </c>
       <c r="C50" t="inlineStr">
         <is>
-          <t>US Core Care Experience Preference Profile</t>
+          <t>US Core Goal Profile</t>
         </is>
       </c>
       <c r="D50" t="inlineStr">
         <is>
-          <t>Care Experience Preference</t>
+          <t>Patient Goal</t>
         </is>
       </c>
       <c r="E50" t="inlineStr">
         <is>
-          <t>Observation</t>
+          <t>Goal</t>
         </is>
       </c>
       <c r="F50" t="inlineStr"/>
       <c r="G50" t="inlineStr"/>
       <c r="H50" t="inlineStr">
         <is>
-          <t>Observation</t>
-        </is>
-      </c>
-      <c r="I50" t="inlineStr"/>
-      <c r="J50" t="inlineStr"/>
+          <t>Goal</t>
+        </is>
+      </c>
+      <c r="I50" t="inlineStr">
+        <is>
+          <t>See Screening and Assessments Guidance</t>
+        </is>
+      </c>
+      <c r="J50" t="inlineStr">
+        <is>
+          <t>screening-and-assessments.html</t>
+        </is>
+      </c>
       <c r="K50" t="inlineStr"/>
       <c r="L50" t="inlineStr"/>
       <c r="M50" t="inlineStr"/>
@@ -2400,26 +2396,32 @@
       <c r="R50" t="inlineStr"/>
     </row>
     <row r="51">
-      <c r="A51" t="n">
-        <v>11</v>
-      </c>
+      <c r="A51" t="inlineStr"/>
       <c r="B51" t="inlineStr">
         <is>
-          <t>Health Insurance Information</t>
+          <t>Goals and Preferences</t>
         </is>
       </c>
       <c r="C51" t="inlineStr">
         <is>
-          <t>US Core Coverage Profile | US Core Organization Profile</t>
-        </is>
-      </c>
-      <c r="D51" t="inlineStr"/>
-      <c r="E51" t="inlineStr"/>
+          <t>US Core Observation ADI Documentation Profile| US Core ADI DocumentReference Profile</t>
+        </is>
+      </c>
+      <c r="D51" t="inlineStr">
+        <is>
+          <t>Advance Directive Observation</t>
+        </is>
+      </c>
+      <c r="E51" t="inlineStr">
+        <is>
+          <t>Observation | DocumentReference</t>
+        </is>
+      </c>
       <c r="F51" t="inlineStr"/>
       <c r="G51" t="inlineStr"/>
       <c r="H51" t="inlineStr">
         <is>
-          <t>Coverage | Organization</t>
+          <t>Observation | DocumentReference</t>
         </is>
       </c>
       <c r="I51" t="inlineStr"/>
@@ -2437,29 +2439,29 @@
       <c r="A52" t="inlineStr"/>
       <c r="B52" t="inlineStr">
         <is>
-          <t>Health Insurance Information</t>
+          <t>Goals and Preferences</t>
         </is>
       </c>
       <c r="C52" t="inlineStr">
         <is>
-          <t>US Core Coverage Profile</t>
+          <t>US Core Treatment Intervention Preference Profile</t>
         </is>
       </c>
       <c r="D52" t="inlineStr">
         <is>
-          <t>Coverage Status</t>
+          <t>Treatment Intervention Preference</t>
         </is>
       </c>
       <c r="E52" t="inlineStr">
         <is>
-          <t>Coverage</t>
+          <t>Observation</t>
         </is>
       </c>
       <c r="F52" t="inlineStr"/>
       <c r="G52" t="inlineStr"/>
       <c r="H52" t="inlineStr">
         <is>
-          <t>Coverage.status+Coverage.period</t>
+          <t>Observation</t>
         </is>
       </c>
       <c r="I52" t="inlineStr"/>
@@ -2477,29 +2479,29 @@
       <c r="A53" t="inlineStr"/>
       <c r="B53" t="inlineStr">
         <is>
-          <t>Health Insurance Information</t>
+          <t>Goals and Preferences</t>
         </is>
       </c>
       <c r="C53" t="inlineStr">
         <is>
-          <t>US Core Coverage Profile</t>
+          <t>US Core Care Experience Preference Profile</t>
         </is>
       </c>
       <c r="D53" t="inlineStr">
         <is>
-          <t>Coverage Type</t>
+          <t>Care Experience Preference</t>
         </is>
       </c>
       <c r="E53" t="inlineStr">
         <is>
-          <t>Coverage</t>
+          <t>Observation</t>
         </is>
       </c>
       <c r="F53" t="inlineStr"/>
       <c r="G53" t="inlineStr"/>
       <c r="H53" t="inlineStr">
         <is>
-          <t>Coverage.type</t>
+          <t>Observation</t>
         </is>
       </c>
       <c r="I53" t="inlineStr"/>
@@ -2514,7 +2516,9 @@
       <c r="R53" t="inlineStr"/>
     </row>
     <row r="54">
-      <c r="A54" t="inlineStr"/>
+      <c r="A54" t="n">
+        <v>11</v>
+      </c>
       <c r="B54" t="inlineStr">
         <is>
           <t>Health Insurance Information</t>
@@ -2522,24 +2526,16 @@
       </c>
       <c r="C54" t="inlineStr">
         <is>
-          <t>US Core Coverage Profile</t>
-        </is>
-      </c>
-      <c r="D54" t="inlineStr">
-        <is>
-          <t>Relationship to Subscriber</t>
-        </is>
-      </c>
-      <c r="E54" t="inlineStr">
-        <is>
-          <t>Coverage</t>
-        </is>
-      </c>
+          <t>US Core Coverage Profile | US Core Organization Profile</t>
+        </is>
+      </c>
+      <c r="D54" t="inlineStr"/>
+      <c r="E54" t="inlineStr"/>
       <c r="F54" t="inlineStr"/>
       <c r="G54" t="inlineStr"/>
       <c r="H54" t="inlineStr">
         <is>
-          <t>Coverage | relationship</t>
+          <t>Coverage | Organization</t>
         </is>
       </c>
       <c r="I54" t="inlineStr"/>
@@ -2567,7 +2563,7 @@
       </c>
       <c r="D55" t="inlineStr">
         <is>
-          <t>Member Identifier</t>
+          <t>Health Insurance Coverage Status</t>
         </is>
       </c>
       <c r="E55" t="inlineStr">
@@ -2579,7 +2575,7 @@
       <c r="G55" t="inlineStr"/>
       <c r="H55" t="inlineStr">
         <is>
-          <t>Coverage.identifier</t>
+          <t>Coverage.status+Coverage.period</t>
         </is>
       </c>
       <c r="I55" t="inlineStr"/>
@@ -2607,7 +2603,7 @@
       </c>
       <c r="D56" t="inlineStr">
         <is>
-          <t>Subscriber Identifier</t>
+          <t>Health Insurance Coverage Type</t>
         </is>
       </c>
       <c r="E56" t="inlineStr">
@@ -2619,7 +2615,7 @@
       <c r="G56" t="inlineStr"/>
       <c r="H56" t="inlineStr">
         <is>
-          <t>Coverage.subscriberId</t>
+          <t>Coverage.type</t>
         </is>
       </c>
       <c r="I56" t="inlineStr"/>
@@ -2647,7 +2643,7 @@
       </c>
       <c r="D57" t="inlineStr">
         <is>
-          <t>Group Number</t>
+          <t>Relationship to Health Insurance Subscriber</t>
         </is>
       </c>
       <c r="E57" t="inlineStr">
@@ -2659,7 +2655,7 @@
       <c r="G57" t="inlineStr"/>
       <c r="H57" t="inlineStr">
         <is>
-          <t>Coverage.class</t>
+          <t>Coverage | relationship</t>
         </is>
       </c>
       <c r="I57" t="inlineStr"/>
@@ -2682,24 +2678,24 @@
       </c>
       <c r="C58" t="inlineStr">
         <is>
-          <t>US Core Coverage Profile | US Core Organization Profile</t>
+          <t>US Core Coverage Profile</t>
         </is>
       </c>
       <c r="D58" t="inlineStr">
         <is>
-          <t>Payer Identifier</t>
+          <t>Health Insurance Member Identifier</t>
         </is>
       </c>
       <c r="E58" t="inlineStr">
         <is>
-          <t>Coverage | Organization</t>
+          <t>Coverage</t>
         </is>
       </c>
       <c r="F58" t="inlineStr"/>
       <c r="G58" t="inlineStr"/>
       <c r="H58" t="inlineStr">
         <is>
-          <t>Coverage.payer | Organization.identifier</t>
+          <t>Coverage.identifier</t>
         </is>
       </c>
       <c r="I58" t="inlineStr"/>
@@ -2714,26 +2710,32 @@
       <c r="R58" t="inlineStr"/>
     </row>
     <row r="59">
-      <c r="A59" t="n">
-        <v>12</v>
-      </c>
+      <c r="A59" t="inlineStr"/>
       <c r="B59" t="inlineStr">
         <is>
-          <t>Health Status Assessments</t>
+          <t>Health Insurance Information</t>
         </is>
       </c>
       <c r="C59" t="inlineStr">
         <is>
-          <t>US Core Simple Observation Profile | US Core Condition Problems and Health Concerns Profile | US Core Observation Screening Assessment Profile | US Core QuestionnaireResponse Profile</t>
-        </is>
-      </c>
-      <c r="D59" t="inlineStr"/>
-      <c r="E59" t="inlineStr"/>
+          <t>US Core Coverage Profile</t>
+        </is>
+      </c>
+      <c r="D59" t="inlineStr">
+        <is>
+          <t>Health Insurance Subscriber Identifier</t>
+        </is>
+      </c>
+      <c r="E59" t="inlineStr">
+        <is>
+          <t>Coverage</t>
+        </is>
+      </c>
       <c r="F59" t="inlineStr"/>
       <c r="G59" t="inlineStr"/>
       <c r="H59" t="inlineStr">
         <is>
-          <t>Observation | Condition | QuestionnaireResponse</t>
+          <t>Coverage.subscriberId</t>
         </is>
       </c>
       <c r="I59" t="inlineStr"/>
@@ -2751,29 +2753,29 @@
       <c r="A60" t="inlineStr"/>
       <c r="B60" t="inlineStr">
         <is>
-          <t>Health Status Assessments</t>
+          <t>Health Insurance Information</t>
         </is>
       </c>
       <c r="C60" t="inlineStr">
         <is>
-          <t>US Core Condition Problems and Health Concerns Profile</t>
+          <t>US Core Coverage Profile</t>
         </is>
       </c>
       <c r="D60" t="inlineStr">
         <is>
-          <t>Health Concerns</t>
+          <t>Health Insurance Group Identifier</t>
         </is>
       </c>
       <c r="E60" t="inlineStr">
         <is>
-          <t>Condition</t>
+          <t>Coverage</t>
         </is>
       </c>
       <c r="F60" t="inlineStr"/>
       <c r="G60" t="inlineStr"/>
       <c r="H60" t="inlineStr">
         <is>
-          <t>Condition</t>
+          <t>Coverage.class</t>
         </is>
       </c>
       <c r="I60" t="inlineStr"/>
@@ -2791,41 +2793,33 @@
       <c r="A61" t="inlineStr"/>
       <c r="B61" t="inlineStr">
         <is>
-          <t>Health Status Assessments</t>
+          <t>Health Insurance Information</t>
         </is>
       </c>
       <c r="C61" t="inlineStr">
         <is>
-          <t>US Core Simple Observation Profile | US Core Condition Problems and Health Concerns Profile | US Core Observation Screening Assessment Profile | US Core QuestionnaireResponse Profile</t>
+          <t>US Core Coverage Profile | US Core Organization Profile</t>
         </is>
       </c>
       <c r="D61" t="inlineStr">
         <is>
-          <t>Functional Status</t>
+          <t>Health Insurance Payer Identifier</t>
         </is>
       </c>
       <c r="E61" t="inlineStr">
         <is>
-          <t>Observation</t>
+          <t>Coverage | Organization</t>
         </is>
       </c>
       <c r="F61" t="inlineStr"/>
       <c r="G61" t="inlineStr"/>
       <c r="H61" t="inlineStr">
         <is>
-          <t>Observation</t>
-        </is>
-      </c>
-      <c r="I61" t="inlineStr">
-        <is>
-          <t>See Screening and Assessments Guidance</t>
-        </is>
-      </c>
-      <c r="J61" t="inlineStr">
-        <is>
-          <t>screening-and-assessments.html</t>
-        </is>
-      </c>
+          <t>Coverage.payer | Organization.identifier</t>
+        </is>
+      </c>
+      <c r="I61" t="inlineStr"/>
+      <c r="J61" t="inlineStr"/>
       <c r="K61" t="inlineStr"/>
       <c r="L61" t="inlineStr"/>
       <c r="M61" t="inlineStr"/>
@@ -2839,41 +2833,33 @@
       <c r="A62" t="inlineStr"/>
       <c r="B62" t="inlineStr">
         <is>
-          <t>Health Status Assessments</t>
+          <t>Health Insurance Information</t>
         </is>
       </c>
       <c r="C62" t="inlineStr">
         <is>
-          <t>US Core Simple Observation Profile | US Core Condition Problems and Health Concerns Profile | US Core Observation Screening Assessment Profile | US Core QuestionnaireResponse Profile</t>
+          <t>US Core Coverage Profile</t>
         </is>
       </c>
       <c r="D62" t="inlineStr">
         <is>
-          <t>Disability Status</t>
+          <t>Health Insurance Coverage Period</t>
         </is>
       </c>
       <c r="E62" t="inlineStr">
         <is>
-          <t>Observation</t>
+          <t>Coverage</t>
         </is>
       </c>
       <c r="F62" t="inlineStr"/>
       <c r="G62" t="inlineStr"/>
       <c r="H62" t="inlineStr">
         <is>
-          <t>Observation</t>
-        </is>
-      </c>
-      <c r="I62" t="inlineStr">
-        <is>
-          <t>See Screening and Assessments Guidance</t>
-        </is>
-      </c>
-      <c r="J62" t="inlineStr">
-        <is>
-          <t>screening-and-assessments.html</t>
-        </is>
-      </c>
+          <t>Coverage.period</t>
+        </is>
+      </c>
+      <c r="I62" t="inlineStr"/>
+      <c r="J62" t="inlineStr"/>
       <c r="K62" t="inlineStr"/>
       <c r="L62" t="inlineStr"/>
       <c r="M62" t="inlineStr"/>
@@ -2887,41 +2873,33 @@
       <c r="A63" t="inlineStr"/>
       <c r="B63" t="inlineStr">
         <is>
-          <t>Health Status Assessments</t>
+          <t>Health Insurance Information</t>
         </is>
       </c>
       <c r="C63" t="inlineStr">
         <is>
-          <t>US Core Simple Observation Profile | US Core Condition Problems and Health Concerns Profile | US Core Observation Screening Assessment Profile | US Core QuestionnaireResponse Profile</t>
+          <t>US Core Coverage Profile</t>
         </is>
       </c>
       <c r="D63" t="inlineStr">
         <is>
-          <t>Mental/Cognitive Status</t>
+          <t>Health Insurance Payer</t>
         </is>
       </c>
       <c r="E63" t="inlineStr">
         <is>
-          <t>Observation</t>
+          <t>Coverage</t>
         </is>
       </c>
       <c r="F63" t="inlineStr"/>
       <c r="G63" t="inlineStr"/>
       <c r="H63" t="inlineStr">
         <is>
-          <t>Observation</t>
-        </is>
-      </c>
-      <c r="I63" t="inlineStr">
-        <is>
-          <t>See Screening and Assessments Guidance</t>
-        </is>
-      </c>
-      <c r="J63" t="inlineStr">
-        <is>
-          <t>screening-and-assessments.html</t>
-        </is>
-      </c>
+          <t>Coverage.payor</t>
+        </is>
+      </c>
+      <c r="I63" t="inlineStr"/>
+      <c r="J63" t="inlineStr"/>
       <c r="K63" t="inlineStr"/>
       <c r="L63" t="inlineStr"/>
       <c r="M63" t="inlineStr"/>
@@ -2935,29 +2913,29 @@
       <c r="A64" t="inlineStr"/>
       <c r="B64" t="inlineStr">
         <is>
-          <t>Health Status Assessments</t>
+          <t>Health Insurance Information</t>
         </is>
       </c>
       <c r="C64" t="inlineStr">
         <is>
-          <t>US Core Observation Pregnancy Status Profile| US Core Observation Pregnancy Intent Profile</t>
+          <t>US Core Coverage Profile</t>
         </is>
       </c>
       <c r="D64" t="inlineStr">
         <is>
-          <t>Pregnancy Status</t>
+          <t>Health Insurance Plan</t>
         </is>
       </c>
       <c r="E64" t="inlineStr">
         <is>
-          <t>Observation</t>
+          <t>Coverage</t>
         </is>
       </c>
       <c r="F64" t="inlineStr"/>
       <c r="G64" t="inlineStr"/>
       <c r="H64" t="inlineStr">
         <is>
-          <t>Observation</t>
+          <t>Coverage.class:plan</t>
         </is>
       </c>
       <c r="I64" t="inlineStr"/>
@@ -2975,41 +2953,33 @@
       <c r="A65" t="inlineStr"/>
       <c r="B65" t="inlineStr">
         <is>
-          <t>Health Status Assessments</t>
+          <t>Health Insurance Information</t>
         </is>
       </c>
       <c r="C65" t="inlineStr">
         <is>
-          <t>US Core Simple Observation Profile | US Core Condition Problems and Health Concerns Profile | US Core Observation Screening Assessment Profile | US Core QuestionnaireResponse Profile</t>
+          <t>US Core Coverage Profile</t>
         </is>
       </c>
       <c r="D65" t="inlineStr">
         <is>
-          <t>Alcohol Use</t>
+          <t>Health Insurance Plan Identifier</t>
         </is>
       </c>
       <c r="E65" t="inlineStr">
         <is>
-          <t>Observation | Condition | QuestionnaireResponse</t>
+          <t>Coverage</t>
         </is>
       </c>
       <c r="F65" t="inlineStr"/>
       <c r="G65" t="inlineStr"/>
       <c r="H65" t="inlineStr">
         <is>
-          <t>Observation | Condition | QuestionnaireResponse</t>
-        </is>
-      </c>
-      <c r="I65" t="inlineStr">
-        <is>
-          <t>See Screening and Assessments Guidance</t>
-        </is>
-      </c>
-      <c r="J65" t="inlineStr">
-        <is>
-          <t>screening-and-assessments.html</t>
-        </is>
-      </c>
+          <t>Coverage.class:plan.value | Coverage.class:plan.name</t>
+        </is>
+      </c>
+      <c r="I65" t="inlineStr"/>
+      <c r="J65" t="inlineStr"/>
       <c r="K65" t="inlineStr"/>
       <c r="L65" t="inlineStr"/>
       <c r="M65" t="inlineStr"/>
@@ -3020,7 +2990,9 @@
       <c r="R65" t="inlineStr"/>
     </row>
     <row r="66">
-      <c r="A66" t="inlineStr"/>
+      <c r="A66" t="n">
+        <v>12</v>
+      </c>
       <c r="B66" t="inlineStr">
         <is>
           <t>Health Status Assessments</t>
@@ -3031,16 +3003,8 @@
           <t>US Core Simple Observation Profile | US Core Condition Problems and Health Concerns Profile | US Core Observation Screening Assessment Profile | US Core QuestionnaireResponse Profile</t>
         </is>
       </c>
-      <c r="D66" t="inlineStr">
-        <is>
-          <t>Substance Use</t>
-        </is>
-      </c>
-      <c r="E66" t="inlineStr">
-        <is>
-          <t>Observation | Condition | QuestionnaireResponse</t>
-        </is>
-      </c>
+      <c r="D66" t="inlineStr"/>
+      <c r="E66" t="inlineStr"/>
       <c r="F66" t="inlineStr"/>
       <c r="G66" t="inlineStr"/>
       <c r="H66" t="inlineStr">
@@ -3048,16 +3012,8 @@
           <t>Observation | Condition | QuestionnaireResponse</t>
         </is>
       </c>
-      <c r="I66" t="inlineStr">
-        <is>
-          <t>See Screening and Assessments Guidance</t>
-        </is>
-      </c>
-      <c r="J66" t="inlineStr">
-        <is>
-          <t>screening-and-assessments.html</t>
-        </is>
-      </c>
+      <c r="I66" t="inlineStr"/>
+      <c r="J66" t="inlineStr"/>
       <c r="K66" t="inlineStr"/>
       <c r="L66" t="inlineStr"/>
       <c r="M66" t="inlineStr"/>
@@ -3081,19 +3037,19 @@
       </c>
       <c r="D67" t="inlineStr">
         <is>
-          <t>Physical Activity</t>
+          <t>Functional Status</t>
         </is>
       </c>
       <c r="E67" t="inlineStr">
         <is>
-          <t>Observation | Condition | QuestionnaireResponse</t>
+          <t>Observation</t>
         </is>
       </c>
       <c r="F67" t="inlineStr"/>
       <c r="G67" t="inlineStr"/>
       <c r="H67" t="inlineStr">
         <is>
-          <t>Observation | Condition | QuestionnaireResponse</t>
+          <t>Observation</t>
         </is>
       </c>
       <c r="I67" t="inlineStr">
@@ -3129,19 +3085,19 @@
       </c>
       <c r="D68" t="inlineStr">
         <is>
-          <t>SDOH Assessment</t>
+          <t>Disability Status</t>
         </is>
       </c>
       <c r="E68" t="inlineStr">
         <is>
-          <t>Observation | Condition | QuestionnaireResponse</t>
+          <t>Observation</t>
         </is>
       </c>
       <c r="F68" t="inlineStr"/>
       <c r="G68" t="inlineStr"/>
       <c r="H68" t="inlineStr">
         <is>
-          <t>Observation | Condition | QuestionnaireResponse</t>
+          <t>Observation</t>
         </is>
       </c>
       <c r="I68" t="inlineStr">
@@ -3172,12 +3128,12 @@
       </c>
       <c r="C69" t="inlineStr">
         <is>
-          <t>US Core Smoking Status Observation Profile</t>
+          <t>US Core Simple Observation Profile | US Core Condition Problems and Health Concerns Profile | US Core Observation Screening Assessment Profile | US Core QuestionnaireResponse Profile</t>
         </is>
       </c>
       <c r="D69" t="inlineStr">
         <is>
-          <t>Smoking Status</t>
+          <t>Mental/Cognitive Status</t>
         </is>
       </c>
       <c r="E69" t="inlineStr">
@@ -3192,8 +3148,16 @@
           <t>Observation</t>
         </is>
       </c>
-      <c r="I69" t="inlineStr"/>
-      <c r="J69" t="inlineStr"/>
+      <c r="I69" t="inlineStr">
+        <is>
+          <t>See Screening and Assessments Guidance</t>
+        </is>
+      </c>
+      <c r="J69" t="inlineStr">
+        <is>
+          <t>screening-and-assessments.html</t>
+        </is>
+      </c>
       <c r="K69" t="inlineStr"/>
       <c r="L69" t="inlineStr"/>
       <c r="M69" t="inlineStr"/>
@@ -3204,26 +3168,32 @@
       <c r="R69" t="inlineStr"/>
     </row>
     <row r="70">
-      <c r="A70" t="n">
-        <v>13</v>
-      </c>
+      <c r="A70" t="inlineStr"/>
       <c r="B70" t="inlineStr">
         <is>
-          <t>Immunizations</t>
+          <t>Health Status Assessments</t>
         </is>
       </c>
       <c r="C70" t="inlineStr">
         <is>
-          <t>US Core Immunization Profile</t>
-        </is>
-      </c>
-      <c r="D70" t="inlineStr"/>
-      <c r="E70" t="inlineStr"/>
+          <t>US Core Observation Pregnancy Status Profile| US Core Observation Pregnancy Intent Profile</t>
+        </is>
+      </c>
+      <c r="D70" t="inlineStr">
+        <is>
+          <t>Pregnancy Status</t>
+        </is>
+      </c>
+      <c r="E70" t="inlineStr">
+        <is>
+          <t>Observation</t>
+        </is>
+      </c>
       <c r="F70" t="inlineStr"/>
       <c r="G70" t="inlineStr"/>
       <c r="H70" t="inlineStr">
         <is>
-          <t>Immunization</t>
+          <t>Observation</t>
         </is>
       </c>
       <c r="I70" t="inlineStr"/>
@@ -3241,33 +3211,41 @@
       <c r="A71" t="inlineStr"/>
       <c r="B71" t="inlineStr">
         <is>
-          <t>Immunizations</t>
+          <t>Health Status Assessments</t>
         </is>
       </c>
       <c r="C71" t="inlineStr">
         <is>
-          <t>US Core Immunization Profile</t>
+          <t>US Core Simple Observation Profile | US Core Condition Problems and Health Concerns Profile | US Core Observation Screening Assessment Profile | US Core QuestionnaireResponse Profile</t>
         </is>
       </c>
       <c r="D71" t="inlineStr">
         <is>
-          <t>Immunizations</t>
+          <t>Alcohol Use</t>
         </is>
       </c>
       <c r="E71" t="inlineStr">
         <is>
-          <t>Immunization</t>
+          <t>Observation | Condition | QuestionnaireResponse</t>
         </is>
       </c>
       <c r="F71" t="inlineStr"/>
       <c r="G71" t="inlineStr"/>
       <c r="H71" t="inlineStr">
         <is>
-          <t>Immunization</t>
-        </is>
-      </c>
-      <c r="I71" t="inlineStr"/>
-      <c r="J71" t="inlineStr"/>
+          <t>Observation | Condition | QuestionnaireResponse</t>
+        </is>
+      </c>
+      <c r="I71" t="inlineStr">
+        <is>
+          <t>See Screening and Assessments Guidance</t>
+        </is>
+      </c>
+      <c r="J71" t="inlineStr">
+        <is>
+          <t>screening-and-assessments.html</t>
+        </is>
+      </c>
       <c r="K71" t="inlineStr"/>
       <c r="L71" t="inlineStr"/>
       <c r="M71" t="inlineStr"/>
@@ -3281,33 +3259,41 @@
       <c r="A72" t="inlineStr"/>
       <c r="B72" t="inlineStr">
         <is>
-          <t>Immunizations</t>
+          <t>Health Status Assessments</t>
         </is>
       </c>
       <c r="C72" t="inlineStr">
         <is>
-          <t>US Core Immunization Profile</t>
+          <t>US Core Simple Observation Profile | US Core Condition Problems and Health Concerns Profile | US Core Observation Screening Assessment Profile | US Core QuestionnaireResponse Profile</t>
         </is>
       </c>
       <c r="D72" t="inlineStr">
         <is>
-          <t>Lot Number</t>
+          <t>Substance Use</t>
         </is>
       </c>
       <c r="E72" t="inlineStr">
         <is>
-          <t>Immunization</t>
+          <t>Observation | Condition | QuestionnaireResponse</t>
         </is>
       </c>
       <c r="F72" t="inlineStr"/>
       <c r="G72" t="inlineStr"/>
       <c r="H72" t="inlineStr">
         <is>
-          <t>Immunization.lotNumber</t>
-        </is>
-      </c>
-      <c r="I72" t="inlineStr"/>
-      <c r="J72" t="inlineStr"/>
+          <t>Observation | Condition | QuestionnaireResponse</t>
+        </is>
+      </c>
+      <c r="I72" t="inlineStr">
+        <is>
+          <t>See Screening and Assessments Guidance</t>
+        </is>
+      </c>
+      <c r="J72" t="inlineStr">
+        <is>
+          <t>screening-and-assessments.html</t>
+        </is>
+      </c>
       <c r="K72" t="inlineStr"/>
       <c r="L72" t="inlineStr"/>
       <c r="M72" t="inlineStr"/>
@@ -3318,30 +3304,44 @@
       <c r="R72" t="inlineStr"/>
     </row>
     <row r="73">
-      <c r="A73" t="n">
-        <v>14</v>
-      </c>
+      <c r="A73" t="inlineStr"/>
       <c r="B73" t="inlineStr">
         <is>
-          <t>Laboratory</t>
+          <t>Health Status Assessments</t>
         </is>
       </c>
       <c r="C73" t="inlineStr">
         <is>
-          <t>US Core Laboratory Result Observation Profile| US Core DiagnosticReport Profile for Laboratory Results Reporting | US Core Specimen Profile</t>
-        </is>
-      </c>
-      <c r="D73" t="inlineStr"/>
-      <c r="E73" t="inlineStr"/>
+          <t>US Core Simple Observation Profile | US Core Condition Problems and Health Concerns Profile | US Core Observation Screening Assessment Profile | US Core QuestionnaireResponse Profile</t>
+        </is>
+      </c>
+      <c r="D73" t="inlineStr">
+        <is>
+          <t>Physical Activity</t>
+        </is>
+      </c>
+      <c r="E73" t="inlineStr">
+        <is>
+          <t>Observation | Condition | QuestionnaireResponse</t>
+        </is>
+      </c>
       <c r="F73" t="inlineStr"/>
       <c r="G73" t="inlineStr"/>
       <c r="H73" t="inlineStr">
         <is>
-          <t>Observation | DiagnosticReport | Specimen</t>
-        </is>
-      </c>
-      <c r="I73" t="inlineStr"/>
-      <c r="J73" t="inlineStr"/>
+          <t>Observation | Condition | QuestionnaireResponse</t>
+        </is>
+      </c>
+      <c r="I73" t="inlineStr">
+        <is>
+          <t>See Screening and Assessments Guidance</t>
+        </is>
+      </c>
+      <c r="J73" t="inlineStr">
+        <is>
+          <t>screening-and-assessments.html</t>
+        </is>
+      </c>
       <c r="K73" t="inlineStr"/>
       <c r="L73" t="inlineStr"/>
       <c r="M73" t="inlineStr"/>
@@ -3355,33 +3355,41 @@
       <c r="A74" t="inlineStr"/>
       <c r="B74" t="inlineStr">
         <is>
-          <t>Laboratory</t>
+          <t>Health Status Assessments</t>
         </is>
       </c>
       <c r="C74" t="inlineStr">
         <is>
-          <t>US Core Laboratory Result Observation Profile| US Core DiagnosticReport Profile for Laboratory Results Reporting</t>
+          <t>US Core Simple Observation Profile | US Core Condition Problems and Health Concerns Profile | US Core Observation Screening Assessment Profile | US Core QuestionnaireResponse Profile</t>
         </is>
       </c>
       <c r="D74" t="inlineStr">
         <is>
-          <t>Tests</t>
+          <t>SDOH Assessment</t>
         </is>
       </c>
       <c r="E74" t="inlineStr">
         <is>
-          <t>Observation | DiagnosticReport</t>
+          <t>Observation | Condition | QuestionnaireResponse</t>
         </is>
       </c>
       <c r="F74" t="inlineStr"/>
       <c r="G74" t="inlineStr"/>
       <c r="H74" t="inlineStr">
         <is>
-          <t>Observation.code | DiagnosticReport.code</t>
-        </is>
-      </c>
-      <c r="I74" t="inlineStr"/>
-      <c r="J74" t="inlineStr"/>
+          <t>Observation | Condition | QuestionnaireResponse</t>
+        </is>
+      </c>
+      <c r="I74" t="inlineStr">
+        <is>
+          <t>See Screening and Assessments Guidance</t>
+        </is>
+      </c>
+      <c r="J74" t="inlineStr">
+        <is>
+          <t>screening-and-assessments.html</t>
+        </is>
+      </c>
       <c r="K74" t="inlineStr"/>
       <c r="L74" t="inlineStr"/>
       <c r="M74" t="inlineStr"/>
@@ -3395,29 +3403,29 @@
       <c r="A75" t="inlineStr"/>
       <c r="B75" t="inlineStr">
         <is>
-          <t>Laboratory</t>
+          <t>Health Status Assessments</t>
         </is>
       </c>
       <c r="C75" t="inlineStr">
         <is>
-          <t>US Core Laboratory Result Observation Profile| US Core DiagnosticReport Profile for Laboratory Results Reporting</t>
+          <t>US Core Tobacco And Nicotine Use Observation Profile</t>
         </is>
       </c>
       <c r="D75" t="inlineStr">
         <is>
-          <t>Values/Results</t>
+          <t>Tobacco and Nicotine Product Use</t>
         </is>
       </c>
       <c r="E75" t="inlineStr">
         <is>
-          <t>Observation | DiagnosticReport</t>
+          <t>Observation</t>
         </is>
       </c>
       <c r="F75" t="inlineStr"/>
       <c r="G75" t="inlineStr"/>
       <c r="H75" t="inlineStr">
         <is>
-          <t>Observation.value[x] | DiagnosticReport.result</t>
+          <t>Observation</t>
         </is>
       </c>
       <c r="I75" t="inlineStr"/>
@@ -3435,33 +3443,41 @@
       <c r="A76" t="inlineStr"/>
       <c r="B76" t="inlineStr">
         <is>
-          <t>Laboratory</t>
+          <t>Health Status Assessments</t>
         </is>
       </c>
       <c r="C76" t="inlineStr">
         <is>
-          <t>US Core Laboratory Result Observation Profile| US Core Specimen Profile</t>
+          <t>US Core Simple Observation Profile | US Core Condition Problems and Health Concerns Profile | US Core Observation Screening Assessment Profile | US Core QuestionnaireResponse Profile</t>
         </is>
       </c>
       <c r="D76" t="inlineStr">
         <is>
-          <t>Specimen Type</t>
+          <t>Nutrition Assessment</t>
         </is>
       </c>
       <c r="E76" t="inlineStr">
         <is>
-          <t>Observation | Specimen</t>
+          <t>Observation | Condition | QuestionnaireResponse</t>
         </is>
       </c>
       <c r="F76" t="inlineStr"/>
       <c r="G76" t="inlineStr"/>
       <c r="H76" t="inlineStr">
         <is>
-          <t>Observation.specimen | Specimen</t>
-        </is>
-      </c>
-      <c r="I76" t="inlineStr"/>
-      <c r="J76" t="inlineStr"/>
+          <t>Observation | Condition | QuestionnaireResponse</t>
+        </is>
+      </c>
+      <c r="I76" t="inlineStr">
+        <is>
+          <t>See Screening and Assessments Guidance</t>
+        </is>
+      </c>
+      <c r="J76" t="inlineStr">
+        <is>
+          <t>screening-and-assessments.html</t>
+        </is>
+      </c>
       <c r="K76" t="inlineStr"/>
       <c r="L76" t="inlineStr"/>
       <c r="M76" t="inlineStr"/>
@@ -3472,32 +3488,26 @@
       <c r="R76" t="inlineStr"/>
     </row>
     <row r="77">
-      <c r="A77" t="inlineStr"/>
+      <c r="A77" t="n">
+        <v>13</v>
+      </c>
       <c r="B77" t="inlineStr">
         <is>
-          <t>Laboratory</t>
+          <t>Healthcare Information Attributes</t>
         </is>
       </c>
       <c r="C77" t="inlineStr">
         <is>
-          <t>US Core Laboratory Result Observation Profile| US Core DiagnosticReport Profile for Laboratory Results Reporting</t>
-        </is>
-      </c>
-      <c r="D77" t="inlineStr">
-        <is>
-          <t>Result Status</t>
-        </is>
-      </c>
-      <c r="E77" t="inlineStr">
-        <is>
-          <t>Observation | DiagnosticReport</t>
-        </is>
-      </c>
+          <t>US Core DiagnosticReport Profile for Laboratory Results Reporting | US Core DiagnosticReport Profile for Report and Note Exchange</t>
+        </is>
+      </c>
+      <c r="D77" t="inlineStr"/>
+      <c r="E77" t="inlineStr"/>
       <c r="F77" t="inlineStr"/>
       <c r="G77" t="inlineStr"/>
       <c r="H77" t="inlineStr">
         <is>
-          <t>Observation.status | DiagnosticReport.status</t>
+          <t>DiagnosticReport</t>
         </is>
       </c>
       <c r="I77" t="inlineStr"/>
@@ -3515,29 +3525,29 @@
       <c r="A78" t="inlineStr"/>
       <c r="B78" t="inlineStr">
         <is>
-          <t>Laboratory</t>
+          <t>Healthcare Information Attributes</t>
         </is>
       </c>
       <c r="C78" t="inlineStr">
         <is>
-          <t>US Core Laboratory Result Observation Profile</t>
+          <t>US Core DiagnosticReport Profile for Laboratory Results Reporting | US Core DiagnosticReport Profile for Report and Note Exchange</t>
         </is>
       </c>
       <c r="D78" t="inlineStr">
         <is>
-          <t>Result Unit of Measure</t>
+          <t>Diagnostic Report Date and Time</t>
         </is>
       </c>
       <c r="E78" t="inlineStr">
         <is>
-          <t>Observation</t>
+          <t>DiagnosticReport</t>
         </is>
       </c>
       <c r="F78" t="inlineStr"/>
       <c r="G78" t="inlineStr"/>
       <c r="H78" t="inlineStr">
         <is>
-          <t>(Observation.value.ofType(Quantity)).code</t>
+          <t>DiagnosticReport.issued</t>
         </is>
       </c>
       <c r="I78" t="inlineStr"/>
@@ -3555,29 +3565,29 @@
       <c r="A79" t="inlineStr"/>
       <c r="B79" t="inlineStr">
         <is>
-          <t>Laboratory</t>
+          <t>Healthcare Information Attributes</t>
         </is>
       </c>
       <c r="C79" t="inlineStr">
         <is>
-          <t>US Core Laboratory Result Observation Profile</t>
+          <t>US Core MedicationRequest Profile</t>
         </is>
       </c>
       <c r="D79" t="inlineStr">
         <is>
-          <t>Result Reference Range</t>
+          <t>Indication</t>
         </is>
       </c>
       <c r="E79" t="inlineStr">
         <is>
-          <t>Observation</t>
+          <t>MedicationRequest</t>
         </is>
       </c>
       <c r="F79" t="inlineStr"/>
       <c r="G79" t="inlineStr"/>
       <c r="H79" t="inlineStr">
         <is>
-          <t>Observation.referenceRange</t>
+          <t>MedicationRequest.reasonCode | Medication.reasonReference</t>
         </is>
       </c>
       <c r="I79" t="inlineStr"/>
@@ -3595,29 +3605,29 @@
       <c r="A80" t="inlineStr"/>
       <c r="B80" t="inlineStr">
         <is>
-          <t>Laboratory</t>
+          <t>Healthcare Information Attributes</t>
         </is>
       </c>
       <c r="C80" t="inlineStr">
         <is>
-          <t>US Core Laboratory Result Observation Profile</t>
+          <t>US Core Procedure Profile|US Core DiagnosticReport Profile for Report and Note Exchange|US Core Immunization Profile</t>
         </is>
       </c>
       <c r="D80" t="inlineStr">
         <is>
-          <t>Result Interpretation</t>
+          <t>Performance Date and Time</t>
         </is>
       </c>
       <c r="E80" t="inlineStr">
         <is>
-          <t>Observation</t>
+          <t>Procedure | DiagnosticReport | Immunization</t>
         </is>
       </c>
       <c r="F80" t="inlineStr"/>
       <c r="G80" t="inlineStr"/>
       <c r="H80" t="inlineStr">
         <is>
-          <t>Observation.interpretation</t>
+          <t>Procedure.performed[x] | DiagnosticReport.effective[x] | Immunization.occurrence[x]</t>
         </is>
       </c>
       <c r="I80" t="inlineStr"/>
@@ -3635,29 +3645,29 @@
       <c r="A81" t="inlineStr"/>
       <c r="B81" t="inlineStr">
         <is>
-          <t>Laboratory</t>
+          <t>Healthcare Information Attributes</t>
         </is>
       </c>
       <c r="C81" t="inlineStr">
         <is>
-          <t>US Core Specimen Profile</t>
+          <t>US Core Immunization Profile | US Core Procedure Profile</t>
         </is>
       </c>
       <c r="D81" t="inlineStr">
         <is>
-          <t>Specimen Identifier</t>
+          <t>Reason Not Performed</t>
         </is>
       </c>
       <c r="E81" t="inlineStr">
         <is>
-          <t>Specimen</t>
+          <t>Immunization | Procedure</t>
         </is>
       </c>
       <c r="F81" t="inlineStr"/>
       <c r="G81" t="inlineStr"/>
       <c r="H81" t="inlineStr">
         <is>
-          <t>Specimen.identifier</t>
+          <t>Immunization.statusReason | Procedure.statusReason</t>
         </is>
       </c>
       <c r="I81" t="inlineStr"/>
@@ -3672,32 +3682,26 @@
       <c r="R81" t="inlineStr"/>
     </row>
     <row r="82">
-      <c r="A82" t="inlineStr"/>
+      <c r="A82" t="n">
+        <v>14</v>
+      </c>
       <c r="B82" t="inlineStr">
         <is>
-          <t>Laboratory</t>
+          <t>Immunizations</t>
         </is>
       </c>
       <c r="C82" t="inlineStr">
         <is>
-          <t>US Core Specimen Profile</t>
-        </is>
-      </c>
-      <c r="D82" t="inlineStr">
-        <is>
-          <t>Specimen Source Site</t>
-        </is>
-      </c>
-      <c r="E82" t="inlineStr">
-        <is>
-          <t>Specimen</t>
-        </is>
-      </c>
+          <t>US Core Immunization Profile</t>
+        </is>
+      </c>
+      <c r="D82" t="inlineStr"/>
+      <c r="E82" t="inlineStr"/>
       <c r="F82" t="inlineStr"/>
       <c r="G82" t="inlineStr"/>
       <c r="H82" t="inlineStr">
         <is>
-          <t>Specimen.collection.bodySite</t>
+          <t>Immunization</t>
         </is>
       </c>
       <c r="I82" t="inlineStr"/>
@@ -3715,29 +3719,29 @@
       <c r="A83" t="inlineStr"/>
       <c r="B83" t="inlineStr">
         <is>
-          <t>Laboratory</t>
+          <t>Immunizations</t>
         </is>
       </c>
       <c r="C83" t="inlineStr">
         <is>
-          <t>US Core Specimen Profile</t>
+          <t>US Core Immunization Profile</t>
         </is>
       </c>
       <c r="D83" t="inlineStr">
         <is>
-          <t>Specimen Condition Acceptability</t>
+          <t>Immunization</t>
         </is>
       </c>
       <c r="E83" t="inlineStr">
         <is>
-          <t>Specimen</t>
+          <t>Immunization</t>
         </is>
       </c>
       <c r="F83" t="inlineStr"/>
       <c r="G83" t="inlineStr"/>
       <c r="H83" t="inlineStr">
         <is>
-          <t>Specimen.condition</t>
+          <t>Immunization</t>
         </is>
       </c>
       <c r="I83" t="inlineStr"/>
@@ -3752,26 +3756,32 @@
       <c r="R83" t="inlineStr"/>
     </row>
     <row r="84">
-      <c r="A84" t="n">
-        <v>15</v>
-      </c>
+      <c r="A84" t="inlineStr"/>
       <c r="B84" t="inlineStr">
         <is>
-          <t>Medical Devices</t>
+          <t>Immunizations</t>
         </is>
       </c>
       <c r="C84" t="inlineStr">
         <is>
-          <t>US Core Device Profile</t>
-        </is>
-      </c>
-      <c r="D84" t="inlineStr"/>
-      <c r="E84" t="inlineStr"/>
+          <t>US Core Immunization Profile</t>
+        </is>
+      </c>
+      <c r="D84" t="inlineStr">
+        <is>
+          <t>Immunization Lot Number</t>
+        </is>
+      </c>
+      <c r="E84" t="inlineStr">
+        <is>
+          <t>Immunization</t>
+        </is>
+      </c>
       <c r="F84" t="inlineStr"/>
       <c r="G84" t="inlineStr"/>
       <c r="H84" t="inlineStr">
         <is>
-          <t>Device</t>
+          <t>Immunization.lotNumber</t>
         </is>
       </c>
       <c r="I84" t="inlineStr"/>
@@ -3789,29 +3799,29 @@
       <c r="A85" t="inlineStr"/>
       <c r="B85" t="inlineStr">
         <is>
-          <t>Medical Devices</t>
+          <t>Immunizations</t>
         </is>
       </c>
       <c r="C85" t="inlineStr">
         <is>
-          <t>US Core Device Profile</t>
+          <t>US Core Immunization Profile</t>
         </is>
       </c>
       <c r="D85" t="inlineStr">
         <is>
-          <t>Unique Device Identifier</t>
+          <t>Immunization Status</t>
         </is>
       </c>
       <c r="E85" t="inlineStr">
         <is>
-          <t>Device</t>
+          <t>Immunization</t>
         </is>
       </c>
       <c r="F85" t="inlineStr"/>
       <c r="G85" t="inlineStr"/>
       <c r="H85" t="inlineStr">
         <is>
-          <t>Device</t>
+          <t>Immunization.status</t>
         </is>
       </c>
       <c r="I85" t="inlineStr"/>
@@ -3826,38 +3836,36 @@
       <c r="R85" t="inlineStr"/>
     </row>
     <row r="86">
-      <c r="A86" t="n">
-        <v>16</v>
-      </c>
+      <c r="A86" t="inlineStr"/>
       <c r="B86" t="inlineStr">
         <is>
-          <t>Medications</t>
+          <t>Immunizations</t>
         </is>
       </c>
       <c r="C86" t="inlineStr">
         <is>
-          <t>US Core MedicationRequest Profile | US Core MedicationDispense Profile | US Core Medication Profile</t>
-        </is>
-      </c>
-      <c r="D86" t="inlineStr"/>
-      <c r="E86" t="inlineStr"/>
+          <t>US Core Immunization Profile</t>
+        </is>
+      </c>
+      <c r="D86" t="inlineStr">
+        <is>
+          <t>Immunization Record Source</t>
+        </is>
+      </c>
+      <c r="E86" t="inlineStr">
+        <is>
+          <t>Immunization</t>
+        </is>
+      </c>
       <c r="F86" t="inlineStr"/>
       <c r="G86" t="inlineStr"/>
       <c r="H86" t="inlineStr">
         <is>
-          <t>MedicationRequest | MedicationDispense | Medication</t>
-        </is>
-      </c>
-      <c r="I86" t="inlineStr">
-        <is>
-          <t>See Medication List Guidance</t>
-        </is>
-      </c>
-      <c r="J86" t="inlineStr">
-        <is>
-          <t>medication-list.html</t>
-        </is>
-      </c>
+          <t>Immunization.primarySource</t>
+        </is>
+      </c>
+      <c r="I86" t="inlineStr"/>
+      <c r="J86" t="inlineStr"/>
       <c r="K86" t="inlineStr"/>
       <c r="L86" t="inlineStr"/>
       <c r="M86" t="inlineStr"/>
@@ -3868,32 +3876,26 @@
       <c r="R86" t="inlineStr"/>
     </row>
     <row r="87">
-      <c r="A87" t="inlineStr"/>
+      <c r="A87" t="n">
+        <v>15</v>
+      </c>
       <c r="B87" t="inlineStr">
         <is>
-          <t>Medications</t>
+          <t>Laboratory</t>
         </is>
       </c>
       <c r="C87" t="inlineStr">
         <is>
-          <t>US Core Medication Profile | US Core MedicationRequest Profile</t>
-        </is>
-      </c>
-      <c r="D87" t="inlineStr">
-        <is>
-          <t>Medications</t>
-        </is>
-      </c>
-      <c r="E87" t="inlineStr">
-        <is>
-          <t>Medication | MedicationRequest</t>
-        </is>
-      </c>
+          <t>US Core Laboratory Result Observation Profile| US Core DiagnosticReport Profile for Laboratory Results Reporting | US Core Specimen Profile</t>
+        </is>
+      </c>
+      <c r="D87" t="inlineStr"/>
+      <c r="E87" t="inlineStr"/>
       <c r="F87" t="inlineStr"/>
       <c r="G87" t="inlineStr"/>
       <c r="H87" t="inlineStr">
         <is>
-          <t>Medication.code | MedicationRequest.medication[x]</t>
+          <t>Observation | DiagnosticReport | Specimen</t>
         </is>
       </c>
       <c r="I87" t="inlineStr"/>
@@ -3911,29 +3913,29 @@
       <c r="A88" t="inlineStr"/>
       <c r="B88" t="inlineStr">
         <is>
-          <t>Medications</t>
+          <t>Laboratory</t>
         </is>
       </c>
       <c r="C88" t="inlineStr">
         <is>
-          <t>US Core MedicationRequest Profile</t>
+          <t>US Core Laboratory Result Observation Profile| US Core DiagnosticReport Profile for Laboratory Results Reporting</t>
         </is>
       </c>
       <c r="D88" t="inlineStr">
         <is>
-          <t>Dose</t>
+          <t>Test</t>
         </is>
       </c>
       <c r="E88" t="inlineStr">
         <is>
-          <t>MedicationRequest</t>
+          <t>Observation | DiagnosticReport</t>
         </is>
       </c>
       <c r="F88" t="inlineStr"/>
       <c r="G88" t="inlineStr"/>
       <c r="H88" t="inlineStr">
         <is>
-          <t>MedicationRequest.dosageInstruction.doseAndRate</t>
+          <t>Observation.code | DiagnosticReport.code</t>
         </is>
       </c>
       <c r="I88" t="inlineStr"/>
@@ -3951,29 +3953,29 @@
       <c r="A89" t="inlineStr"/>
       <c r="B89" t="inlineStr">
         <is>
-          <t>Medications</t>
+          <t>Laboratory</t>
         </is>
       </c>
       <c r="C89" t="inlineStr">
         <is>
-          <t>US Core MedicationRequest Profile</t>
+          <t>US Core Laboratory Result Observation Profile| US Core DiagnosticReport Profile for Laboratory Results Reporting</t>
         </is>
       </c>
       <c r="D89" t="inlineStr">
         <is>
-          <t>Dose Unit of Measure</t>
+          <t>Value/Result</t>
         </is>
       </c>
       <c r="E89" t="inlineStr">
         <is>
-          <t>MedicationRequest</t>
+          <t>Observation | DiagnosticReport</t>
         </is>
       </c>
       <c r="F89" t="inlineStr"/>
       <c r="G89" t="inlineStr"/>
       <c r="H89" t="inlineStr">
         <is>
-          <t>MedicationRequest.dosageInstruction.doseAndRate</t>
+          <t>Observation.value[x] | DiagnosticReport.result</t>
         </is>
       </c>
       <c r="I89" t="inlineStr"/>
@@ -3991,29 +3993,29 @@
       <c r="A90" t="inlineStr"/>
       <c r="B90" t="inlineStr">
         <is>
-          <t>Medications</t>
+          <t>Laboratory</t>
         </is>
       </c>
       <c r="C90" t="inlineStr">
         <is>
-          <t>US Core MedicationRequest Profile | US Core MedicationDispense Profile</t>
+          <t>US Core Laboratory Result Observation Profile| US Core Specimen Profile</t>
         </is>
       </c>
       <c r="D90" t="inlineStr">
         <is>
-          <t>Route of Administration</t>
+          <t>Specimen Type</t>
         </is>
       </c>
       <c r="E90" t="inlineStr">
         <is>
-          <t>MedicationRequest | MedicationDispense</t>
+          <t>Observation | Specimen</t>
         </is>
       </c>
       <c r="F90" t="inlineStr"/>
       <c r="G90" t="inlineStr"/>
       <c r="H90" t="inlineStr">
         <is>
-          <t>MedicationRequest.dosageInstruction.route | MedicationDispense.dosageInstruction.route</t>
+          <t>Observation.specimen | Specimen</t>
         </is>
       </c>
       <c r="I90" t="inlineStr"/>
@@ -4031,29 +4033,29 @@
       <c r="A91" t="inlineStr"/>
       <c r="B91" t="inlineStr">
         <is>
-          <t>Medications</t>
+          <t>Laboratory</t>
         </is>
       </c>
       <c r="C91" t="inlineStr">
         <is>
-          <t>US Core MedicationRequest Profile</t>
+          <t>US Core Laboratory Result Observation Profile| US Core DiagnosticReport Profile for Laboratory Results Reporting</t>
         </is>
       </c>
       <c r="D91" t="inlineStr">
         <is>
-          <t>Indication</t>
+          <t>Result Status</t>
         </is>
       </c>
       <c r="E91" t="inlineStr">
         <is>
-          <t>MedicationRequest</t>
+          <t>Observation | DiagnosticReport</t>
         </is>
       </c>
       <c r="F91" t="inlineStr"/>
       <c r="G91" t="inlineStr"/>
       <c r="H91" t="inlineStr">
         <is>
-          <t>MedicationRequest.reasonCode | Medication.reasonReference</t>
+          <t>Observation.status | DiagnosticReport.status</t>
         </is>
       </c>
       <c r="I91" t="inlineStr"/>
@@ -4071,29 +4073,29 @@
       <c r="A92" t="inlineStr"/>
       <c r="B92" t="inlineStr">
         <is>
-          <t>Medications</t>
+          <t>Laboratory</t>
         </is>
       </c>
       <c r="C92" t="inlineStr">
         <is>
-          <t>US Core MedicationRequest Profile</t>
+          <t>US Core Laboratory Result Observation Profile</t>
         </is>
       </c>
       <c r="D92" t="inlineStr">
         <is>
-          <t>Medication Instructions</t>
+          <t>Result Unit of Measure</t>
         </is>
       </c>
       <c r="E92" t="inlineStr">
         <is>
-          <t>MedicationRequest</t>
+          <t>Observation</t>
         </is>
       </c>
       <c r="F92" t="inlineStr"/>
       <c r="G92" t="inlineStr"/>
       <c r="H92" t="inlineStr">
         <is>
-          <t>MedicationRequest.dosageInstruction</t>
+          <t>(Observation.value.ofType(Quantity)).code</t>
         </is>
       </c>
       <c r="I92" t="inlineStr"/>
@@ -4111,33 +4113,29 @@
       <c r="A93" t="inlineStr"/>
       <c r="B93" t="inlineStr">
         <is>
-          <t>Medications</t>
+          <t>Laboratory</t>
         </is>
       </c>
       <c r="C93" t="inlineStr">
         <is>
-          <t>US Core MedicationRequest Profile | US Core Medication Adherence Extension</t>
+          <t>US Core Laboratory Result Observation Profile</t>
         </is>
       </c>
       <c r="D93" t="inlineStr">
         <is>
-          <t>Medication Adherence</t>
+          <t>Result Reference Range</t>
         </is>
       </c>
       <c r="E93" t="inlineStr">
         <is>
-          <t>MedicationRequest</t>
-        </is>
-      </c>
-      <c r="F93" t="inlineStr">
-        <is>
-          <t>US Core Medication Adherence Extension</t>
-        </is>
-      </c>
+          <t>Observation</t>
+        </is>
+      </c>
+      <c r="F93" t="inlineStr"/>
       <c r="G93" t="inlineStr"/>
       <c r="H93" t="inlineStr">
         <is>
-          <t>MedicationRequest.extension.where(url='Patient.extension.where(url='http://hl7.org/fhir/us/core/StructureDefinition/us-core-medication-adherence')</t>
+          <t>Observation.referenceRange</t>
         </is>
       </c>
       <c r="I93" t="inlineStr"/>
@@ -4155,29 +4153,29 @@
       <c r="A94" t="inlineStr"/>
       <c r="B94" t="inlineStr">
         <is>
-          <t>Medications</t>
+          <t>Laboratory</t>
         </is>
       </c>
       <c r="C94" t="inlineStr">
         <is>
-          <t>US Core MedicationDispense Profile</t>
+          <t>US Core Laboratory Result Observation Profile</t>
         </is>
       </c>
       <c r="D94" t="inlineStr">
         <is>
-          <t>Fill Status</t>
+          <t>Result Interpretation</t>
         </is>
       </c>
       <c r="E94" t="inlineStr">
         <is>
-          <t>MedicationDispense</t>
+          <t>Observation</t>
         </is>
       </c>
       <c r="F94" t="inlineStr"/>
       <c r="G94" t="inlineStr"/>
       <c r="H94" t="inlineStr">
         <is>
-          <t>MedicationDispense</t>
+          <t>Observation.interpretation</t>
         </is>
       </c>
       <c r="I94" t="inlineStr"/>
@@ -4192,26 +4190,32 @@
       <c r="R94" t="inlineStr"/>
     </row>
     <row r="95">
-      <c r="A95" t="n">
-        <v>17</v>
-      </c>
+      <c r="A95" t="inlineStr"/>
       <c r="B95" t="inlineStr">
         <is>
-          <t>Orders</t>
+          <t>Laboratory</t>
         </is>
       </c>
       <c r="C95" t="inlineStr">
         <is>
-          <t>US Core MedicationRequest Profile | US Core ServiceRequest Profile | US Core ADI DocumentReference Profile</t>
-        </is>
-      </c>
-      <c r="D95" t="inlineStr"/>
-      <c r="E95" t="inlineStr"/>
+          <t>US Core Specimen Profile</t>
+        </is>
+      </c>
+      <c r="D95" t="inlineStr">
+        <is>
+          <t>Specimen Identifier</t>
+        </is>
+      </c>
+      <c r="E95" t="inlineStr">
+        <is>
+          <t>Specimen</t>
+        </is>
+      </c>
       <c r="F95" t="inlineStr"/>
       <c r="G95" t="inlineStr"/>
       <c r="H95" t="inlineStr">
         <is>
-          <t>MedicationRequest | ServiceRequest</t>
+          <t>Specimen.identifier</t>
         </is>
       </c>
       <c r="I95" t="inlineStr"/>
@@ -4229,29 +4233,29 @@
       <c r="A96" t="inlineStr"/>
       <c r="B96" t="inlineStr">
         <is>
-          <t>Orders</t>
+          <t>Laboratory</t>
         </is>
       </c>
       <c r="C96" t="inlineStr">
         <is>
-          <t>US Core MedicationRequest Profile</t>
+          <t>US Core Specimen Profile</t>
         </is>
       </c>
       <c r="D96" t="inlineStr">
         <is>
-          <t>Medication Order</t>
+          <t>Specimen Source Site</t>
         </is>
       </c>
       <c r="E96" t="inlineStr">
         <is>
-          <t>MedicationRequest</t>
+          <t>Specimen</t>
         </is>
       </c>
       <c r="F96" t="inlineStr"/>
       <c r="G96" t="inlineStr"/>
       <c r="H96" t="inlineStr">
         <is>
-          <t>MedicationRequest</t>
+          <t>Specimen.collection.bodySite</t>
         </is>
       </c>
       <c r="I96" t="inlineStr"/>
@@ -4269,29 +4273,29 @@
       <c r="A97" t="inlineStr"/>
       <c r="B97" t="inlineStr">
         <is>
-          <t>Orders</t>
+          <t>Laboratory</t>
         </is>
       </c>
       <c r="C97" t="inlineStr">
         <is>
-          <t>US Core ServiceRequest Profile</t>
+          <t>US Core Specimen Profile</t>
         </is>
       </c>
       <c r="D97" t="inlineStr">
         <is>
-          <t>Laboratory Order</t>
+          <t>Specimen Condition</t>
         </is>
       </c>
       <c r="E97" t="inlineStr">
         <is>
-          <t>ServiceRequest</t>
+          <t>Specimen</t>
         </is>
       </c>
       <c r="F97" t="inlineStr"/>
       <c r="G97" t="inlineStr"/>
       <c r="H97" t="inlineStr">
         <is>
-          <t>ServiceRequest</t>
+          <t>Specimen.condition</t>
         </is>
       </c>
       <c r="I97" t="inlineStr"/>
@@ -4309,29 +4313,29 @@
       <c r="A98" t="inlineStr"/>
       <c r="B98" t="inlineStr">
         <is>
-          <t>Orders</t>
+          <t>Laboratory</t>
         </is>
       </c>
       <c r="C98" t="inlineStr">
         <is>
-          <t>US Core ServiceRequest Profile</t>
+          <t>US Core Specimen Profile| US Core Laboratory Result Observation Profile</t>
         </is>
       </c>
       <c r="D98" t="inlineStr">
         <is>
-          <t>Diagnostic Imaging Order</t>
+          <t>Specimen Collection Date and Time</t>
         </is>
       </c>
       <c r="E98" t="inlineStr">
         <is>
-          <t>ServiceRequest</t>
+          <t>Specimen | Observation</t>
         </is>
       </c>
       <c r="F98" t="inlineStr"/>
       <c r="G98" t="inlineStr"/>
       <c r="H98" t="inlineStr">
         <is>
-          <t>ServiceRequest</t>
+          <t>Specimen.collection.collected[x] | Observation.effective[x]</t>
         </is>
       </c>
       <c r="I98" t="inlineStr"/>
@@ -4349,29 +4353,29 @@
       <c r="A99" t="inlineStr"/>
       <c r="B99" t="inlineStr">
         <is>
-          <t>Orders</t>
+          <t>Laboratory</t>
         </is>
       </c>
       <c r="C99" t="inlineStr">
         <is>
-          <t>US Core ServiceRequest Profile</t>
+          <t>US Core Specimen Profile</t>
         </is>
       </c>
       <c r="D99" t="inlineStr">
         <is>
-          <t>Clinical Test Order</t>
+          <t>Specimen Collection Method</t>
         </is>
       </c>
       <c r="E99" t="inlineStr">
         <is>
-          <t>ServiceRequest</t>
+          <t>Specimen</t>
         </is>
       </c>
       <c r="F99" t="inlineStr"/>
       <c r="G99" t="inlineStr"/>
       <c r="H99" t="inlineStr">
         <is>
-          <t>ServiceRequest</t>
+          <t>Specimen.collection.method</t>
         </is>
       </c>
       <c r="I99" t="inlineStr"/>
@@ -4386,32 +4390,26 @@
       <c r="R99" t="inlineStr"/>
     </row>
     <row r="100">
-      <c r="A100" t="inlineStr"/>
+      <c r="A100" t="n">
+        <v>16</v>
+      </c>
       <c r="B100" t="inlineStr">
         <is>
-          <t>Orders</t>
+          <t>Medical Devices</t>
         </is>
       </c>
       <c r="C100" t="inlineStr">
         <is>
-          <t>US Core ServiceRequest Profile</t>
-        </is>
-      </c>
-      <c r="D100" t="inlineStr">
-        <is>
-          <t>Procedure Order</t>
-        </is>
-      </c>
-      <c r="E100" t="inlineStr">
-        <is>
-          <t>ServiceRequest</t>
-        </is>
-      </c>
+          <t>US Core Device Profile</t>
+        </is>
+      </c>
+      <c r="D100" t="inlineStr"/>
+      <c r="E100" t="inlineStr"/>
       <c r="F100" t="inlineStr"/>
       <c r="G100" t="inlineStr"/>
       <c r="H100" t="inlineStr">
         <is>
-          <t>ServiceRequest</t>
+          <t>Device</t>
         </is>
       </c>
       <c r="I100" t="inlineStr"/>
@@ -4429,29 +4427,29 @@
       <c r="A101" t="inlineStr"/>
       <c r="B101" t="inlineStr">
         <is>
-          <t>Orders</t>
+          <t>Medical Devices</t>
         </is>
       </c>
       <c r="C101" t="inlineStr">
         <is>
-          <t>US Core ADI DocumentReference Profile</t>
+          <t>US Core Device Profile</t>
         </is>
       </c>
       <c r="D101" t="inlineStr">
         <is>
-          <t>Portable Medical Order</t>
+          <t>Unique Device Identifier</t>
         </is>
       </c>
       <c r="E101" t="inlineStr">
         <is>
-          <t>ServiceRequest | DocumentReference</t>
+          <t>Device</t>
         </is>
       </c>
       <c r="F101" t="inlineStr"/>
       <c r="G101" t="inlineStr"/>
       <c r="H101" t="inlineStr">
         <is>
-          <t>ServiceRequest | DocumentReference</t>
+          <t>Device</t>
         </is>
       </c>
       <c r="I101" t="inlineStr"/>
@@ -4466,26 +4464,32 @@
       <c r="R101" t="inlineStr"/>
     </row>
     <row r="102">
-      <c r="A102" t="n">
-        <v>18</v>
-      </c>
+      <c r="A102" t="inlineStr"/>
       <c r="B102" t="inlineStr">
         <is>
-          <t>Patient Demographics</t>
+          <t>Medical Devices</t>
         </is>
       </c>
       <c r="C102" t="inlineStr">
         <is>
-          <t>US Core Patient Profile | US Core RelatedPerson Profile | US Core Observation Occupation Profile</t>
-        </is>
-      </c>
-      <c r="D102" t="inlineStr"/>
-      <c r="E102" t="inlineStr"/>
+          <t>US Core Device Profile</t>
+        </is>
+      </c>
+      <c r="D102" t="inlineStr">
+        <is>
+          <t>Device Type</t>
+        </is>
+      </c>
+      <c r="E102" t="inlineStr">
+        <is>
+          <t>Device</t>
+        </is>
+      </c>
       <c r="F102" t="inlineStr"/>
       <c r="G102" t="inlineStr"/>
       <c r="H102" t="inlineStr">
         <is>
-          <t>Patient | Observation</t>
+          <t>Device.type</t>
         </is>
       </c>
       <c r="I102" t="inlineStr"/>
@@ -4500,36 +4504,38 @@
       <c r="R102" t="inlineStr"/>
     </row>
     <row r="103">
-      <c r="A103" t="inlineStr"/>
+      <c r="A103" t="n">
+        <v>17</v>
+      </c>
       <c r="B103" t="inlineStr">
         <is>
-          <t>Patient Demographics</t>
+          <t>Medications</t>
         </is>
       </c>
       <c r="C103" t="inlineStr">
         <is>
-          <t>US Core Patient Profile</t>
-        </is>
-      </c>
-      <c r="D103" t="inlineStr">
-        <is>
-          <t>First Name</t>
-        </is>
-      </c>
-      <c r="E103" t="inlineStr">
-        <is>
-          <t>Patient</t>
-        </is>
-      </c>
+          <t>US Core MedicationRequest Profile | US Core MedicationDispense Profile | US Core Medication Profile</t>
+        </is>
+      </c>
+      <c r="D103" t="inlineStr"/>
+      <c r="E103" t="inlineStr"/>
       <c r="F103" t="inlineStr"/>
       <c r="G103" t="inlineStr"/>
       <c r="H103" t="inlineStr">
         <is>
-          <t>Patient.name.given</t>
-        </is>
-      </c>
-      <c r="I103" t="inlineStr"/>
-      <c r="J103" t="inlineStr"/>
+          <t>MedicationRequest | MedicationDispense | Medication</t>
+        </is>
+      </c>
+      <c r="I103" t="inlineStr">
+        <is>
+          <t>See Medication List Guidance</t>
+        </is>
+      </c>
+      <c r="J103" t="inlineStr">
+        <is>
+          <t>medication-list.html</t>
+        </is>
+      </c>
       <c r="K103" t="inlineStr"/>
       <c r="L103" t="inlineStr"/>
       <c r="M103" t="inlineStr"/>
@@ -4543,29 +4549,29 @@
       <c r="A104" t="inlineStr"/>
       <c r="B104" t="inlineStr">
         <is>
-          <t>Patient Demographics</t>
+          <t>Medications</t>
         </is>
       </c>
       <c r="C104" t="inlineStr">
         <is>
-          <t>US Core Patient Profile</t>
+          <t>US Core Medication Profile | US Core MedicationRequest Profile</t>
         </is>
       </c>
       <c r="D104" t="inlineStr">
         <is>
-          <t>Last Name</t>
+          <t>Medication</t>
         </is>
       </c>
       <c r="E104" t="inlineStr">
         <is>
-          <t>Patient</t>
+          <t>Medication | MedicationRequest</t>
         </is>
       </c>
       <c r="F104" t="inlineStr"/>
       <c r="G104" t="inlineStr"/>
       <c r="H104" t="inlineStr">
         <is>
-          <t>Patient.name.family</t>
+          <t>Medication.code | MedicationRequest.medication[x]</t>
         </is>
       </c>
       <c r="I104" t="inlineStr"/>
@@ -4583,29 +4589,29 @@
       <c r="A105" t="inlineStr"/>
       <c r="B105" t="inlineStr">
         <is>
-          <t>Patient Demographics</t>
+          <t>Medications</t>
         </is>
       </c>
       <c r="C105" t="inlineStr">
         <is>
-          <t>US Core Patient Profile</t>
+          <t>US Core MedicationRequest Profile</t>
         </is>
       </c>
       <c r="D105" t="inlineStr">
         <is>
-          <t>Previous Name</t>
+          <t>Dose</t>
         </is>
       </c>
       <c r="E105" t="inlineStr">
         <is>
-          <t>Patient</t>
+          <t>MedicationRequest</t>
         </is>
       </c>
       <c r="F105" t="inlineStr"/>
       <c r="G105" t="inlineStr"/>
       <c r="H105" t="inlineStr">
         <is>
-          <t>Patient.name.use</t>
+          <t>MedicationRequest.dosageInstruction.doseAndRate</t>
         </is>
       </c>
       <c r="I105" t="inlineStr"/>
@@ -4623,29 +4629,29 @@
       <c r="A106" t="inlineStr"/>
       <c r="B106" t="inlineStr">
         <is>
-          <t>Patient Demographics</t>
+          <t>Medications</t>
         </is>
       </c>
       <c r="C106" t="inlineStr">
         <is>
-          <t>US Core Patient Profile</t>
+          <t>US Core MedicationRequest Profile</t>
         </is>
       </c>
       <c r="D106" t="inlineStr">
         <is>
-          <t>Middle Name (including middle initial)</t>
+          <t>Dose Unit of Measure</t>
         </is>
       </c>
       <c r="E106" t="inlineStr">
         <is>
-          <t>Patient</t>
+          <t>MedicationRequest</t>
         </is>
       </c>
       <c r="F106" t="inlineStr"/>
       <c r="G106" t="inlineStr"/>
       <c r="H106" t="inlineStr">
         <is>
-          <t>Patient.name.given</t>
+          <t>MedicationRequest.dosageInstruction.doseAndRate</t>
         </is>
       </c>
       <c r="I106" t="inlineStr"/>
@@ -4663,29 +4669,29 @@
       <c r="A107" t="inlineStr"/>
       <c r="B107" t="inlineStr">
         <is>
-          <t>Patient Demographics</t>
+          <t>Medications</t>
         </is>
       </c>
       <c r="C107" t="inlineStr">
         <is>
-          <t>US Core Patient Profile</t>
+          <t>US Core MedicationRequest Profile | US Core MedicationDispense Profile</t>
         </is>
       </c>
       <c r="D107" t="inlineStr">
         <is>
-          <t>Suffix</t>
+          <t>Route of Administration</t>
         </is>
       </c>
       <c r="E107" t="inlineStr">
         <is>
-          <t>Patient</t>
+          <t>MedicationRequest | MedicationDispense</t>
         </is>
       </c>
       <c r="F107" t="inlineStr"/>
       <c r="G107" t="inlineStr"/>
       <c r="H107" t="inlineStr">
         <is>
-          <t>Patient.name.suffix</t>
+          <t>MedicationRequest.dosageInstruction.route | MedicationDispense.dosageInstruction.route</t>
         </is>
       </c>
       <c r="I107" t="inlineStr"/>
@@ -4703,33 +4709,29 @@
       <c r="A108" t="inlineStr"/>
       <c r="B108" t="inlineStr">
         <is>
-          <t>Patient Demographics</t>
+          <t>Medications</t>
         </is>
       </c>
       <c r="C108" t="inlineStr">
         <is>
-          <t>US Core Patient Profile | US Core Individual Sex Extension</t>
+          <t>US Core MedicationRequest Profile</t>
         </is>
       </c>
       <c r="D108" t="inlineStr">
         <is>
-          <t>Sex</t>
+          <t>Medication Instructions</t>
         </is>
       </c>
       <c r="E108" t="inlineStr">
         <is>
-          <t>Patient</t>
-        </is>
-      </c>
-      <c r="F108" t="inlineStr">
-        <is>
-          <t>US Core Individual Sex Extension</t>
-        </is>
-      </c>
+          <t>MedicationRequest</t>
+        </is>
+      </c>
+      <c r="F108" t="inlineStr"/>
       <c r="G108" t="inlineStr"/>
       <c r="H108" t="inlineStr">
         <is>
-          <t>Patient.extension.where(url='http://hl7.org/fhir/us/core/StructureDefinition/us-core-individual-sex')</t>
+          <t>MedicationRequest.dosageInstruction</t>
         </is>
       </c>
       <c r="I108" t="inlineStr"/>
@@ -4747,29 +4749,33 @@
       <c r="A109" t="inlineStr"/>
       <c r="B109" t="inlineStr">
         <is>
-          <t>Patient Demographics</t>
+          <t>Medications</t>
         </is>
       </c>
       <c r="C109" t="inlineStr">
         <is>
-          <t>US Core Patient Profile</t>
+          <t>US Core MedicationRequest Profile | US Core Medication Adherence Extension</t>
         </is>
       </c>
       <c r="D109" t="inlineStr">
         <is>
-          <t>Date of Birth</t>
+          <t>Medication Adherence</t>
         </is>
       </c>
       <c r="E109" t="inlineStr">
         <is>
-          <t>Patient</t>
-        </is>
-      </c>
-      <c r="F109" t="inlineStr"/>
+          <t>MedicationRequest</t>
+        </is>
+      </c>
+      <c r="F109" t="inlineStr">
+        <is>
+          <t>US Core Medication Adherence Extension</t>
+        </is>
+      </c>
       <c r="G109" t="inlineStr"/>
       <c r="H109" t="inlineStr">
         <is>
-          <t>Patient.birthDate</t>
+          <t>MedicationRequest.extension.where(url='Patient.extension.where(url='http://hl7.org/fhir/us/core/StructureDefinition/us-core-medication-adherence')</t>
         </is>
       </c>
       <c r="I109" t="inlineStr"/>
@@ -4787,29 +4793,29 @@
       <c r="A110" t="inlineStr"/>
       <c r="B110" t="inlineStr">
         <is>
-          <t>Patient Demographics</t>
+          <t>Medications</t>
         </is>
       </c>
       <c r="C110" t="inlineStr">
         <is>
-          <t>US Core Patient Profile</t>
+          <t>US Core MedicationAdministration Profile</t>
         </is>
       </c>
       <c r="D110" t="inlineStr">
         <is>
-          <t>Date of Death</t>
+          <t>Medication Administration</t>
         </is>
       </c>
       <c r="E110" t="inlineStr">
         <is>
-          <t>Patient</t>
+          <t>MedicationAdministration</t>
         </is>
       </c>
       <c r="F110" t="inlineStr"/>
       <c r="G110" t="inlineStr"/>
       <c r="H110" t="inlineStr">
         <is>
-          <t>Patient.deceased[x]</t>
+          <t>MedicationAdministration</t>
         </is>
       </c>
       <c r="I110" t="inlineStr"/>
@@ -4827,33 +4833,29 @@
       <c r="A111" t="inlineStr"/>
       <c r="B111" t="inlineStr">
         <is>
-          <t>Patient Demographics</t>
+          <t>Medications</t>
         </is>
       </c>
       <c r="C111" t="inlineStr">
         <is>
-          <t>US Core Patient Profile | US Core Race Extension</t>
+          <t>US Core MedicationDispense Profile</t>
         </is>
       </c>
       <c r="D111" t="inlineStr">
         <is>
-          <t>Race</t>
+          <t>Medication Dispense Status</t>
         </is>
       </c>
       <c r="E111" t="inlineStr">
         <is>
-          <t>Patient</t>
-        </is>
-      </c>
-      <c r="F111" t="inlineStr">
-        <is>
-          <t>US Core Race Extension</t>
-        </is>
-      </c>
+          <t>MedicationDispense</t>
+        </is>
+      </c>
+      <c r="F111" t="inlineStr"/>
       <c r="G111" t="inlineStr"/>
       <c r="H111" t="inlineStr">
         <is>
-          <t>Patient.extension.where(url='http://hl7.org/fhir/us/core/StructureDefinition/us-core-race')</t>
+          <t>MedicationDispense</t>
         </is>
       </c>
       <c r="I111" t="inlineStr"/>
@@ -4871,33 +4873,29 @@
       <c r="A112" t="inlineStr"/>
       <c r="B112" t="inlineStr">
         <is>
-          <t>Patient Demographics</t>
+          <t>Medications</t>
         </is>
       </c>
       <c r="C112" t="inlineStr">
         <is>
-          <t>US Core Patient Profile | US Core Ethnicity Extension</t>
+          <t>US Core MedicationRequest Profile | US Core MedicationDispense Profile</t>
         </is>
       </c>
       <c r="D112" t="inlineStr">
         <is>
-          <t>Ethnicity</t>
+          <t>Medication Dispense Quantity</t>
         </is>
       </c>
       <c r="E112" t="inlineStr">
         <is>
-          <t>Patient</t>
-        </is>
-      </c>
-      <c r="F112" t="inlineStr">
-        <is>
-          <t>US Core Ethnicity Extension</t>
-        </is>
-      </c>
+          <t>MedicationRequest | MedicationDispense</t>
+        </is>
+      </c>
+      <c r="F112" t="inlineStr"/>
       <c r="G112" t="inlineStr"/>
       <c r="H112" t="inlineStr">
         <is>
-          <t>Patient.extension.where(url='http://hl7.org/fhir/us/core/StructureDefinition/us-core-ethnicity')</t>
+          <t>MedicationRequest.dispenseRequest.quantity | MedicationDispense.quantity</t>
         </is>
       </c>
       <c r="I112" t="inlineStr"/>
@@ -4912,36 +4910,26 @@
       <c r="R112" t="inlineStr"/>
     </row>
     <row r="113">
-      <c r="A113" t="inlineStr"/>
+      <c r="A113" t="n">
+        <v>18</v>
+      </c>
       <c r="B113" t="inlineStr">
         <is>
-          <t>Patient Demographics</t>
+          <t>Orders</t>
         </is>
       </c>
       <c r="C113" t="inlineStr">
         <is>
-          <t>US Core Patient Profile | US Core Tribal Affiliation Extension</t>
-        </is>
-      </c>
-      <c r="D113" t="inlineStr">
-        <is>
-          <t>Tribal Affiliation</t>
-        </is>
-      </c>
-      <c r="E113" t="inlineStr">
-        <is>
-          <t>Patient</t>
-        </is>
-      </c>
-      <c r="F113" t="inlineStr">
-        <is>
-          <t>US Core Tibal Affiliation Extension</t>
-        </is>
-      </c>
+          <t>US Core MedicationRequest Profile | US Core ServiceRequest Profile | US Core ADI DocumentReference Profile | US Core DeviceRequest Profile | US Core NutritionOrder Profile</t>
+        </is>
+      </c>
+      <c r="D113" t="inlineStr"/>
+      <c r="E113" t="inlineStr"/>
+      <c r="F113" t="inlineStr"/>
       <c r="G113" t="inlineStr"/>
       <c r="H113" t="inlineStr">
         <is>
-          <t>Patient.extension.where(url='http://hl7.org/fhir/us/core/StructureDefinition/us-core-tribal-affiliation')</t>
+          <t>MedicationRequest | ServiceRequest</t>
         </is>
       </c>
       <c r="I113" t="inlineStr"/>
@@ -4959,29 +4947,29 @@
       <c r="A114" t="inlineStr"/>
       <c r="B114" t="inlineStr">
         <is>
-          <t>Patient Demographics</t>
+          <t>Orders</t>
         </is>
       </c>
       <c r="C114" t="inlineStr">
         <is>
-          <t>US Core Patient Profile</t>
+          <t>US Core MedicationRequest Profile</t>
         </is>
       </c>
       <c r="D114" t="inlineStr">
         <is>
-          <t>Preferred Language</t>
+          <t>Medication Order</t>
         </is>
       </c>
       <c r="E114" t="inlineStr">
         <is>
-          <t>Patient</t>
+          <t>MedicationRequest</t>
         </is>
       </c>
       <c r="F114" t="inlineStr"/>
       <c r="G114" t="inlineStr"/>
       <c r="H114" t="inlineStr">
         <is>
-          <t>Patient.communication</t>
+          <t>MedicationRequest</t>
         </is>
       </c>
       <c r="I114" t="inlineStr"/>
@@ -4999,33 +4987,29 @@
       <c r="A115" t="inlineStr"/>
       <c r="B115" t="inlineStr">
         <is>
-          <t>Patient Demographics</t>
+          <t>Orders</t>
         </is>
       </c>
       <c r="C115" t="inlineStr">
         <is>
-          <t>US Core Patient Profile | US Core Encounter Profile |US Core Interpreter Needed Extension</t>
+          <t>US Core ServiceRequest Profile</t>
         </is>
       </c>
       <c r="D115" t="inlineStr">
         <is>
-          <t>Interpreter Needed</t>
+          <t>Laboratory Order</t>
         </is>
       </c>
       <c r="E115" t="inlineStr">
         <is>
-          <t>Patient | Encounter</t>
-        </is>
-      </c>
-      <c r="F115" t="inlineStr">
-        <is>
-          <t>US Core Interpreter Needed Extension</t>
-        </is>
-      </c>
+          <t>ServiceRequest</t>
+        </is>
+      </c>
+      <c r="F115" t="inlineStr"/>
       <c r="G115" t="inlineStr"/>
       <c r="H115" t="inlineStr">
         <is>
-          <t>Patient.extension.where(url='http://hl7.org/fhir/us/core/StructureDefinition/us-core-interpreter-needed'') | Encounter.extension.where(url='http://hl7.org/fhir/us/core/StructureDefinition/us-core-interpreter-needed'')</t>
+          <t>ServiceRequest</t>
         </is>
       </c>
       <c r="I115" t="inlineStr"/>
@@ -5043,29 +5027,29 @@
       <c r="A116" t="inlineStr"/>
       <c r="B116" t="inlineStr">
         <is>
-          <t>Patient Demographics</t>
+          <t>Orders</t>
         </is>
       </c>
       <c r="C116" t="inlineStr">
         <is>
-          <t>US Core Patient Profile</t>
+          <t>US Core ServiceRequest Profile</t>
         </is>
       </c>
       <c r="D116" t="inlineStr">
         <is>
-          <t>Address</t>
+          <t>Diagnostic Imaging Order</t>
         </is>
       </c>
       <c r="E116" t="inlineStr">
         <is>
-          <t>Patient</t>
+          <t>ServiceRequest</t>
         </is>
       </c>
       <c r="F116" t="inlineStr"/>
       <c r="G116" t="inlineStr"/>
       <c r="H116" t="inlineStr">
         <is>
-          <t>Patient.address</t>
+          <t>ServiceRequest</t>
         </is>
       </c>
       <c r="I116" t="inlineStr"/>
@@ -5083,29 +5067,29 @@
       <c r="A117" t="inlineStr"/>
       <c r="B117" t="inlineStr">
         <is>
-          <t>Patient Demographics</t>
+          <t>Orders</t>
         </is>
       </c>
       <c r="C117" t="inlineStr">
         <is>
-          <t>US Core Patient Profile</t>
+          <t>US Core ServiceRequest Profile</t>
         </is>
       </c>
       <c r="D117" t="inlineStr">
         <is>
-          <t>Previous Address</t>
+          <t>Clinical Test Order</t>
         </is>
       </c>
       <c r="E117" t="inlineStr">
         <is>
-          <t>Patient</t>
+          <t>ServiceRequest</t>
         </is>
       </c>
       <c r="F117" t="inlineStr"/>
       <c r="G117" t="inlineStr"/>
       <c r="H117" t="inlineStr">
         <is>
-          <t>Patient.address</t>
+          <t>ServiceRequest</t>
         </is>
       </c>
       <c r="I117" t="inlineStr"/>
@@ -5123,29 +5107,29 @@
       <c r="A118" t="inlineStr"/>
       <c r="B118" t="inlineStr">
         <is>
-          <t>Patient Demographics</t>
+          <t>Orders</t>
         </is>
       </c>
       <c r="C118" t="inlineStr">
         <is>
-          <t>US Core Patient Profile</t>
+          <t>US Core ServiceRequest Profile</t>
         </is>
       </c>
       <c r="D118" t="inlineStr">
         <is>
-          <t>Email</t>
+          <t>Procedure Order</t>
         </is>
       </c>
       <c r="E118" t="inlineStr">
         <is>
-          <t>Patient</t>
+          <t>ServiceRequest</t>
         </is>
       </c>
       <c r="F118" t="inlineStr"/>
       <c r="G118" t="inlineStr"/>
       <c r="H118" t="inlineStr">
         <is>
-          <t>Patient.telecom</t>
+          <t>ServiceRequest</t>
         </is>
       </c>
       <c r="I118" t="inlineStr"/>
@@ -5163,29 +5147,29 @@
       <c r="A119" t="inlineStr"/>
       <c r="B119" t="inlineStr">
         <is>
-          <t>Patient Demographics</t>
+          <t>Orders</t>
         </is>
       </c>
       <c r="C119" t="inlineStr">
         <is>
-          <t>US Core Patient Profile</t>
+          <t>US Core ADI DocumentReference Profile</t>
         </is>
       </c>
       <c r="D119" t="inlineStr">
         <is>
-          <t>Phone Number</t>
+          <t>Portable Medical Order</t>
         </is>
       </c>
       <c r="E119" t="inlineStr">
         <is>
-          <t>Patient</t>
+          <t>ServiceRequest | DocumentReference</t>
         </is>
       </c>
       <c r="F119" t="inlineStr"/>
       <c r="G119" t="inlineStr"/>
       <c r="H119" t="inlineStr">
         <is>
-          <t>Patient.telecom</t>
+          <t>ServiceRequest | DocumentReference</t>
         </is>
       </c>
       <c r="I119" t="inlineStr"/>
@@ -5203,29 +5187,29 @@
       <c r="A120" t="inlineStr"/>
       <c r="B120" t="inlineStr">
         <is>
-          <t>Patient Demographics</t>
+          <t>Orders</t>
         </is>
       </c>
       <c r="C120" t="inlineStr">
         <is>
-          <t>US Core RelatedPerson Profile</t>
+          <t>US Core ServiceRequest Profile</t>
         </is>
       </c>
       <c r="D120" t="inlineStr">
         <is>
-          <t>Related Person's Name</t>
+          <t>Referral Order</t>
         </is>
       </c>
       <c r="E120" t="inlineStr">
         <is>
-          <t>RelatedPerson</t>
+          <t>ServiceRequest</t>
         </is>
       </c>
       <c r="F120" t="inlineStr"/>
       <c r="G120" t="inlineStr"/>
       <c r="H120" t="inlineStr">
         <is>
-          <t>RelatedPerson.name</t>
+          <t>ServiceRequest</t>
         </is>
       </c>
       <c r="I120" t="inlineStr"/>
@@ -5243,29 +5227,29 @@
       <c r="A121" t="inlineStr"/>
       <c r="B121" t="inlineStr">
         <is>
-          <t>Patient Demographics</t>
+          <t>Orders</t>
         </is>
       </c>
       <c r="C121" t="inlineStr">
         <is>
-          <t>US Core RelatedPerson Profile</t>
+          <t>US Core DeviceRequest Profile</t>
         </is>
       </c>
       <c r="D121" t="inlineStr">
         <is>
-          <t>Related Person's Relationship</t>
+          <t>Medical Device Order</t>
         </is>
       </c>
       <c r="E121" t="inlineStr">
         <is>
-          <t>RelatedPerson</t>
+          <t>DeviceRequest</t>
         </is>
       </c>
       <c r="F121" t="inlineStr"/>
       <c r="G121" t="inlineStr"/>
       <c r="H121" t="inlineStr">
         <is>
-          <t>RelatedPerson.relationship</t>
+          <t>DeviceRequest</t>
         </is>
       </c>
       <c r="I121" t="inlineStr"/>
@@ -5283,29 +5267,29 @@
       <c r="A122" t="inlineStr"/>
       <c r="B122" t="inlineStr">
         <is>
-          <t>Patient Demographics</t>
+          <t>Orders</t>
         </is>
       </c>
       <c r="C122" t="inlineStr">
         <is>
-          <t>US Core Observation Occupation Profile</t>
+          <t>US Core NutritionOrder Profile</t>
         </is>
       </c>
       <c r="D122" t="inlineStr">
         <is>
-          <t>Occupation</t>
+          <t>Nutrition Order</t>
         </is>
       </c>
       <c r="E122" t="inlineStr">
         <is>
-          <t>Observation</t>
+          <t>NutritionOrder</t>
         </is>
       </c>
       <c r="F122" t="inlineStr"/>
       <c r="G122" t="inlineStr"/>
       <c r="H122" t="inlineStr">
         <is>
-          <t>Observation</t>
+          <t>NutritionOrder</t>
         </is>
       </c>
       <c r="I122" t="inlineStr"/>
@@ -5320,32 +5304,26 @@
       <c r="R122" t="inlineStr"/>
     </row>
     <row r="123">
-      <c r="A123" t="inlineStr"/>
+      <c r="A123" t="n">
+        <v>19</v>
+      </c>
       <c r="B123" t="inlineStr">
         <is>
-          <t>Patient Demographics</t>
+          <t>Patient Demographics/Information</t>
         </is>
       </c>
       <c r="C123" t="inlineStr">
         <is>
-          <t>US Core Observation Occupation Profile</t>
-        </is>
-      </c>
-      <c r="D123" t="inlineStr">
-        <is>
-          <t>Occupation Industry</t>
-        </is>
-      </c>
-      <c r="E123" t="inlineStr">
-        <is>
-          <t>Observation</t>
-        </is>
-      </c>
+          <t>US Core Patient Profile | US Core RelatedPerson Profile | US Core Observation Occupation Profile</t>
+        </is>
+      </c>
+      <c r="D123" t="inlineStr"/>
+      <c r="E123" t="inlineStr"/>
       <c r="F123" t="inlineStr"/>
       <c r="G123" t="inlineStr"/>
       <c r="H123" t="inlineStr">
         <is>
-          <t>Observation</t>
+          <t>Patient | Observation</t>
         </is>
       </c>
       <c r="I123" t="inlineStr"/>
@@ -5360,30 +5338,32 @@
       <c r="R123" t="inlineStr"/>
     </row>
     <row r="124">
-      <c r="A124" t="n">
-        <v>19</v>
-      </c>
+      <c r="A124" t="inlineStr"/>
       <c r="B124" t="inlineStr">
         <is>
-          <t>Problems</t>
+          <t>Patient Demographics/Information</t>
         </is>
       </c>
       <c r="C124" t="inlineStr">
         <is>
-          <t>US Core Condition Problems and Health Concerns Profile</t>
-        </is>
-      </c>
-      <c r="D124" t="inlineStr"/>
+          <t>US Core Patient Profile</t>
+        </is>
+      </c>
+      <c r="D124" t="inlineStr">
+        <is>
+          <t>First Name</t>
+        </is>
+      </c>
       <c r="E124" t="inlineStr">
         <is>
-          <t>Condition</t>
+          <t>Patient</t>
         </is>
       </c>
       <c r="F124" t="inlineStr"/>
       <c r="G124" t="inlineStr"/>
       <c r="H124" t="inlineStr">
         <is>
-          <t>Condition</t>
+          <t>Patient.name.given</t>
         </is>
       </c>
       <c r="I124" t="inlineStr"/>
@@ -5401,29 +5381,29 @@
       <c r="A125" t="inlineStr"/>
       <c r="B125" t="inlineStr">
         <is>
-          <t>Problems</t>
+          <t>Patient Demographics/Information</t>
         </is>
       </c>
       <c r="C125" t="inlineStr">
         <is>
-          <t>US Core Condition Problems and Health Concerns Profile</t>
+          <t>US Core Patient Profile</t>
         </is>
       </c>
       <c r="D125" t="inlineStr">
         <is>
-          <t>Date of Resolution</t>
+          <t>Last Name</t>
         </is>
       </c>
       <c r="E125" t="inlineStr">
         <is>
-          <t>Condition</t>
+          <t>Patient</t>
         </is>
       </c>
       <c r="F125" t="inlineStr"/>
       <c r="G125" t="inlineStr"/>
       <c r="H125" t="inlineStr">
         <is>
-          <t>Condition.abatement[x]</t>
+          <t>Patient.name.family</t>
         </is>
       </c>
       <c r="I125" t="inlineStr"/>
@@ -5441,37 +5421,29 @@
       <c r="A126" t="inlineStr"/>
       <c r="B126" t="inlineStr">
         <is>
-          <t>Problems</t>
+          <t>Patient Demographics/Information</t>
         </is>
       </c>
       <c r="C126" t="inlineStr">
         <is>
-          <t>US Core Condition Problems and Health Concerns Profile |assertedDate Extension</t>
+          <t>US Core Patient Profile</t>
         </is>
       </c>
       <c r="D126" t="inlineStr">
         <is>
-          <t>Date of Diagnosis</t>
+          <t>Previous Name</t>
         </is>
       </c>
       <c r="E126" t="inlineStr">
         <is>
-          <t>Condition</t>
-        </is>
-      </c>
-      <c r="F126" t="inlineStr">
-        <is>
-          <t>assertedDate Extension</t>
-        </is>
-      </c>
-      <c r="G126" t="inlineStr">
-        <is>
-          <t>StructureDefinition-condition-assertedDate.html</t>
-        </is>
-      </c>
+          <t>Patient</t>
+        </is>
+      </c>
+      <c r="F126" t="inlineStr"/>
+      <c r="G126" t="inlineStr"/>
       <c r="H126" t="inlineStr">
         <is>
-          <t>Condition.extension.where(url='http://hl7.org/fhir/StructureDefinition/condition-assertedDate') | Condition.onset[x] | Condition.onsetDate</t>
+          <t>Patient.name.use</t>
         </is>
       </c>
       <c r="I126" t="inlineStr"/>
@@ -5489,29 +5461,29 @@
       <c r="A127" t="inlineStr"/>
       <c r="B127" t="inlineStr">
         <is>
-          <t>Problems</t>
+          <t>Patient Demographics/Information</t>
         </is>
       </c>
       <c r="C127" t="inlineStr">
         <is>
-          <t>US Core Condition Problems and Health Concerns Profile</t>
+          <t>US Core Patient Profile</t>
         </is>
       </c>
       <c r="D127" t="inlineStr">
         <is>
-          <t>Date of Onset</t>
+          <t>Middle Name (including middle initial)</t>
         </is>
       </c>
       <c r="E127" t="inlineStr">
         <is>
-          <t>Condition</t>
+          <t>Patient</t>
         </is>
       </c>
       <c r="F127" t="inlineStr"/>
       <c r="G127" t="inlineStr"/>
       <c r="H127" t="inlineStr">
         <is>
-          <t>Condition.onset[x]</t>
+          <t>Patient.name.given</t>
         </is>
       </c>
       <c r="I127" t="inlineStr"/>
@@ -5529,41 +5501,33 @@
       <c r="A128" t="inlineStr"/>
       <c r="B128" t="inlineStr">
         <is>
-          <t>Problems</t>
+          <t>Patient Demographics/Information</t>
         </is>
       </c>
       <c r="C128" t="inlineStr">
         <is>
-          <t>US Core Condition Problems and Health Concerns Profile</t>
+          <t>US Core Patient Profile</t>
         </is>
       </c>
       <c r="D128" t="inlineStr">
         <is>
-          <t>SDOH Problems/Health Concerns</t>
+          <t>Name Suffix</t>
         </is>
       </c>
       <c r="E128" t="inlineStr">
         <is>
-          <t>Condition</t>
+          <t>Patient</t>
         </is>
       </c>
       <c r="F128" t="inlineStr"/>
       <c r="G128" t="inlineStr"/>
       <c r="H128" t="inlineStr">
         <is>
-          <t>Condition</t>
-        </is>
-      </c>
-      <c r="I128" t="inlineStr">
-        <is>
-          <t>See Screening and Assessments Guidance</t>
-        </is>
-      </c>
-      <c r="J128" t="inlineStr">
-        <is>
-          <t>screening-and-assessments.html</t>
-        </is>
-      </c>
+          <t>Patient.name.suffix</t>
+        </is>
+      </c>
+      <c r="I128" t="inlineStr"/>
+      <c r="J128" t="inlineStr"/>
       <c r="K128" t="inlineStr"/>
       <c r="L128" t="inlineStr"/>
       <c r="M128" t="inlineStr"/>
@@ -5574,26 +5538,36 @@
       <c r="R128" t="inlineStr"/>
     </row>
     <row r="129">
-      <c r="A129" t="n">
-        <v>20</v>
-      </c>
+      <c r="A129" t="inlineStr"/>
       <c r="B129" t="inlineStr">
         <is>
-          <t>Procedures</t>
+          <t>Patient Demographics/Information</t>
         </is>
       </c>
       <c r="C129" t="inlineStr">
         <is>
-          <t>US Core Procedure Profile | US Core ServiceRequest Profile</t>
-        </is>
-      </c>
-      <c r="D129" t="inlineStr"/>
-      <c r="E129" t="inlineStr"/>
-      <c r="F129" t="inlineStr"/>
+          <t>US Core Patient Profile | US Core Individual Sex Extension</t>
+        </is>
+      </c>
+      <c r="D129" t="inlineStr">
+        <is>
+          <t>Sex</t>
+        </is>
+      </c>
+      <c r="E129" t="inlineStr">
+        <is>
+          <t>Patient</t>
+        </is>
+      </c>
+      <c r="F129" t="inlineStr">
+        <is>
+          <t>US Core Individual Sex Extension</t>
+        </is>
+      </c>
       <c r="G129" t="inlineStr"/>
       <c r="H129" t="inlineStr">
         <is>
-          <t>Procedure | ServiceRequest</t>
+          <t>Patient.extension.where(url='http://hl7.org/fhir/us/core/StructureDefinition/us-core-individual-sex')</t>
         </is>
       </c>
       <c r="I129" t="inlineStr"/>
@@ -5611,29 +5585,29 @@
       <c r="A130" t="inlineStr"/>
       <c r="B130" t="inlineStr">
         <is>
-          <t>Procedures</t>
+          <t>Patient Demographics/Information</t>
         </is>
       </c>
       <c r="C130" t="inlineStr">
         <is>
-          <t>US Core Procedure Profile</t>
+          <t>US Core Patient Profile</t>
         </is>
       </c>
       <c r="D130" t="inlineStr">
         <is>
-          <t>Procedure</t>
+          <t>Date of Birth</t>
         </is>
       </c>
       <c r="E130" t="inlineStr">
         <is>
-          <t>Procedure</t>
+          <t>Patient</t>
         </is>
       </c>
       <c r="F130" t="inlineStr"/>
       <c r="G130" t="inlineStr"/>
       <c r="H130" t="inlineStr">
         <is>
-          <t>Procedure</t>
+          <t>Patient.birthDate</t>
         </is>
       </c>
       <c r="I130" t="inlineStr"/>
@@ -5651,29 +5625,29 @@
       <c r="A131" t="inlineStr"/>
       <c r="B131" t="inlineStr">
         <is>
-          <t>Procedures</t>
+          <t>Patient Demographics/Information</t>
         </is>
       </c>
       <c r="C131" t="inlineStr">
         <is>
-          <t>US Core Procedure Profile|US Core DiagnosticReport Profile for Report and Note Exchange|US Core Immunization Profile</t>
+          <t>US Core Patient Profile</t>
         </is>
       </c>
       <c r="D131" t="inlineStr">
         <is>
-          <t>Performance Time</t>
+          <t>Date of Death</t>
         </is>
       </c>
       <c r="E131" t="inlineStr">
         <is>
-          <t>Procedure | DiagnosticRepor | Immunization</t>
+          <t>Patient</t>
         </is>
       </c>
       <c r="F131" t="inlineStr"/>
       <c r="G131" t="inlineStr"/>
       <c r="H131" t="inlineStr">
         <is>
-          <t>Procedure.pertormed[x] | DiagnosticReport.effective[x] | Immunization.occurrence[x]</t>
+          <t>Patient.deceased[x]</t>
         </is>
       </c>
       <c r="I131" t="inlineStr"/>
@@ -5691,29 +5665,33 @@
       <c r="A132" t="inlineStr"/>
       <c r="B132" t="inlineStr">
         <is>
-          <t>Procedures</t>
+          <t>Patient Demographics/Information</t>
         </is>
       </c>
       <c r="C132" t="inlineStr">
         <is>
-          <t>US Core ServiceRequest Profile | US Core Procedure Profile</t>
+          <t>US Core Patient Profile | US Core Race Extension</t>
         </is>
       </c>
       <c r="D132" t="inlineStr">
         <is>
-          <t>Reason for Referral</t>
+          <t>Race</t>
         </is>
       </c>
       <c r="E132" t="inlineStr">
         <is>
-          <t>ServiceRequest | Procedure</t>
-        </is>
-      </c>
-      <c r="F132" t="inlineStr"/>
+          <t>Patient</t>
+        </is>
+      </c>
+      <c r="F132" t="inlineStr">
+        <is>
+          <t>US Core Race Extension</t>
+        </is>
+      </c>
       <c r="G132" t="inlineStr"/>
       <c r="H132" t="inlineStr">
         <is>
-          <t>ServiceRequest.reasonCode | ServiceRequest.reasonReference | Procedure.reasonCode | Procedure.reasonReference</t>
+          <t>Patient.extension.where(url='http://hl7.org/fhir/us/core/StructureDefinition/us-core-race')</t>
         </is>
       </c>
       <c r="I132" t="inlineStr"/>
@@ -5731,41 +5709,37 @@
       <c r="A133" t="inlineStr"/>
       <c r="B133" t="inlineStr">
         <is>
-          <t>Procedures</t>
+          <t>Patient Demographics/Information</t>
         </is>
       </c>
       <c r="C133" t="inlineStr">
         <is>
-          <t>US Core ServiceRequest Profile | US Core Procedure Profile</t>
+          <t>US Core Patient Profile | US Core Ethnicity Extension</t>
         </is>
       </c>
       <c r="D133" t="inlineStr">
         <is>
-          <t>SDOH Interventions</t>
+          <t>Ethnicity</t>
         </is>
       </c>
       <c r="E133" t="inlineStr">
         <is>
-          <t>ServiceRequest | Procedure</t>
-        </is>
-      </c>
-      <c r="F133" t="inlineStr"/>
+          <t>Patient</t>
+        </is>
+      </c>
+      <c r="F133" t="inlineStr">
+        <is>
+          <t>US Core Ethnicity Extension</t>
+        </is>
+      </c>
       <c r="G133" t="inlineStr"/>
       <c r="H133" t="inlineStr">
         <is>
-          <t>ServiceRequest | Procedure</t>
-        </is>
-      </c>
-      <c r="I133" t="inlineStr">
-        <is>
-          <t>See Screening and Assessments Guidance</t>
-        </is>
-      </c>
-      <c r="J133" t="inlineStr">
-        <is>
-          <t>screening-and-assessments.html</t>
-        </is>
-      </c>
+          <t>Patient.extension.where(url='http://hl7.org/fhir/us/core/StructureDefinition/us-core-ethnicity')</t>
+        </is>
+      </c>
+      <c r="I133" t="inlineStr"/>
+      <c r="J133" t="inlineStr"/>
       <c r="K133" t="inlineStr"/>
       <c r="L133" t="inlineStr"/>
       <c r="M133" t="inlineStr"/>
@@ -5776,38 +5750,40 @@
       <c r="R133" t="inlineStr"/>
     </row>
     <row r="134">
-      <c r="A134" t="n">
-        <v>21</v>
-      </c>
+      <c r="A134" t="inlineStr"/>
       <c r="B134" t="inlineStr">
         <is>
-          <t>Provenance</t>
+          <t>Patient Demographics/Information</t>
         </is>
       </c>
       <c r="C134" t="inlineStr">
         <is>
-          <t>US Core Provenance Profile</t>
-        </is>
-      </c>
-      <c r="D134" t="inlineStr"/>
-      <c r="E134" t="inlineStr"/>
-      <c r="F134" t="inlineStr"/>
+          <t>US Core Patient Profile | US Core Tribal Affiliation Extension</t>
+        </is>
+      </c>
+      <c r="D134" t="inlineStr">
+        <is>
+          <t>Tribal Affiliation</t>
+        </is>
+      </c>
+      <c r="E134" t="inlineStr">
+        <is>
+          <t>Patient</t>
+        </is>
+      </c>
+      <c r="F134" t="inlineStr">
+        <is>
+          <t>US Core Tibal Affiliation Extension</t>
+        </is>
+      </c>
       <c r="G134" t="inlineStr"/>
       <c r="H134" t="inlineStr">
         <is>
-          <t>Provenance</t>
-        </is>
-      </c>
-      <c r="I134" t="inlineStr">
-        <is>
-          <t>See Basic Provenance Guidance</t>
-        </is>
-      </c>
-      <c r="J134" t="inlineStr">
-        <is>
-          <t>basic-provenance.html</t>
-        </is>
-      </c>
+          <t>Patient.extension.where(url='http://hl7.org/fhir/us/core/StructureDefinition/us-core-tribal-affiliation')</t>
+        </is>
+      </c>
+      <c r="I134" t="inlineStr"/>
+      <c r="J134" t="inlineStr"/>
       <c r="K134" t="inlineStr"/>
       <c r="L134" t="inlineStr"/>
       <c r="M134" t="inlineStr"/>
@@ -5821,21 +5797,29 @@
       <c r="A135" t="inlineStr"/>
       <c r="B135" t="inlineStr">
         <is>
-          <t>Provenance</t>
-        </is>
-      </c>
-      <c r="C135" t="inlineStr"/>
+          <t>Patient Demographics/Information</t>
+        </is>
+      </c>
+      <c r="C135" t="inlineStr">
+        <is>
+          <t>US Core Patient Profile</t>
+        </is>
+      </c>
       <c r="D135" t="inlineStr">
         <is>
-          <t>Author</t>
-        </is>
-      </c>
-      <c r="E135" t="inlineStr"/>
+          <t>Preferred Language</t>
+        </is>
+      </c>
+      <c r="E135" t="inlineStr">
+        <is>
+          <t>Patient</t>
+        </is>
+      </c>
       <c r="F135" t="inlineStr"/>
       <c r="G135" t="inlineStr"/>
       <c r="H135" t="inlineStr">
         <is>
-          <t>Provenance.recorded</t>
+          <t>Patient.communication</t>
         </is>
       </c>
       <c r="I135" t="inlineStr"/>
@@ -5853,21 +5837,33 @@
       <c r="A136" t="inlineStr"/>
       <c r="B136" t="inlineStr">
         <is>
-          <t>Provenance</t>
-        </is>
-      </c>
-      <c r="C136" t="inlineStr"/>
+          <t>Patient Demographics/Information</t>
+        </is>
+      </c>
+      <c r="C136" t="inlineStr">
+        <is>
+          <t>US Core Patient Profile | US Core Encounter Profile |US Core Interpreter Needed Extension</t>
+        </is>
+      </c>
       <c r="D136" t="inlineStr">
         <is>
-          <t>Author Role</t>
-        </is>
-      </c>
-      <c r="E136" t="inlineStr"/>
-      <c r="F136" t="inlineStr"/>
+          <t>Interpreter Needed</t>
+        </is>
+      </c>
+      <c r="E136" t="inlineStr">
+        <is>
+          <t>Patient | Encounter</t>
+        </is>
+      </c>
+      <c r="F136" t="inlineStr">
+        <is>
+          <t>US Core Interpreter Needed Extension</t>
+        </is>
+      </c>
       <c r="G136" t="inlineStr"/>
       <c r="H136" t="inlineStr">
         <is>
-          <t>Provenance.agent</t>
+          <t>Patient.extension.where(url='http://hl7.org/fhir/us/core/StructureDefinition/us-core-interpreter-needed'') | Encounter.extension.where(url='http://hl7.org/fhir/us/core/StructureDefinition/us-core-interpreter-needed'')</t>
         </is>
       </c>
       <c r="I136" t="inlineStr"/>
@@ -5885,25 +5881,29 @@
       <c r="A137" t="inlineStr"/>
       <c r="B137" t="inlineStr">
         <is>
-          <t>Provenance</t>
+          <t>Patient Demographics/Information</t>
         </is>
       </c>
       <c r="C137" t="inlineStr">
         <is>
-          <t>US Core Provenance Profile</t>
+          <t>US Core Patient Profile</t>
         </is>
       </c>
       <c r="D137" t="inlineStr">
         <is>
-          <t>Author Time Stamp</t>
-        </is>
-      </c>
-      <c r="E137" t="inlineStr"/>
+          <t>Current Address</t>
+        </is>
+      </c>
+      <c r="E137" t="inlineStr">
+        <is>
+          <t>Patient</t>
+        </is>
+      </c>
       <c r="F137" t="inlineStr"/>
       <c r="G137" t="inlineStr"/>
       <c r="H137" t="inlineStr">
         <is>
-          <t>Provenance.recorded</t>
+          <t>Patient.address</t>
         </is>
       </c>
       <c r="I137" t="inlineStr"/>
@@ -5921,25 +5921,29 @@
       <c r="A138" t="inlineStr"/>
       <c r="B138" t="inlineStr">
         <is>
-          <t>Provenance</t>
+          <t>Patient Demographics/Information</t>
         </is>
       </c>
       <c r="C138" t="inlineStr">
         <is>
-          <t>US Core Provenance Profile</t>
+          <t>US Core Patient Profile</t>
         </is>
       </c>
       <c r="D138" t="inlineStr">
         <is>
-          <t>Author Organization</t>
-        </is>
-      </c>
-      <c r="E138" t="inlineStr"/>
+          <t>Previous Address</t>
+        </is>
+      </c>
+      <c r="E138" t="inlineStr">
+        <is>
+          <t>Patient</t>
+        </is>
+      </c>
       <c r="F138" t="inlineStr"/>
       <c r="G138" t="inlineStr"/>
       <c r="H138" t="inlineStr">
         <is>
-          <t>Provenance.agent</t>
+          <t>Patient.address</t>
         </is>
       </c>
       <c r="I138" t="inlineStr"/>
@@ -5954,26 +5958,32 @@
       <c r="R138" t="inlineStr"/>
     </row>
     <row r="139">
-      <c r="A139" t="n">
-        <v>22</v>
-      </c>
+      <c r="A139" t="inlineStr"/>
       <c r="B139" t="inlineStr">
         <is>
-          <t>Vital Signs</t>
+          <t>Patient Demographics/Information</t>
         </is>
       </c>
       <c r="C139" t="inlineStr">
         <is>
-          <t>US Core Vital Signs Profile</t>
-        </is>
-      </c>
-      <c r="D139" t="inlineStr"/>
-      <c r="E139" t="inlineStr"/>
+          <t>US Core Patient Profile</t>
+        </is>
+      </c>
+      <c r="D139" t="inlineStr">
+        <is>
+          <t>Email Address</t>
+        </is>
+      </c>
+      <c r="E139" t="inlineStr">
+        <is>
+          <t>Patient</t>
+        </is>
+      </c>
       <c r="F139" t="inlineStr"/>
       <c r="G139" t="inlineStr"/>
       <c r="H139" t="inlineStr">
         <is>
-          <t>Observation</t>
+          <t>Patient.telecom</t>
         </is>
       </c>
       <c r="I139" t="inlineStr"/>
@@ -5991,29 +6001,29 @@
       <c r="A140" t="inlineStr"/>
       <c r="B140" t="inlineStr">
         <is>
-          <t>Vital Signs</t>
+          <t>Patient Demographics/Information</t>
         </is>
       </c>
       <c r="C140" t="inlineStr">
         <is>
-          <t>US Core Average Blood Pressure Profile</t>
+          <t>US Core Patient Profile</t>
         </is>
       </c>
       <c r="D140" t="inlineStr">
         <is>
-          <t>Average Blood Pressure</t>
+          <t>Phone Number</t>
         </is>
       </c>
       <c r="E140" t="inlineStr">
         <is>
-          <t>Observation</t>
+          <t>Patient</t>
         </is>
       </c>
       <c r="F140" t="inlineStr"/>
       <c r="G140" t="inlineStr"/>
       <c r="H140" t="inlineStr">
         <is>
-          <t>Observation</t>
+          <t>Patient.telecom</t>
         </is>
       </c>
       <c r="I140" t="inlineStr"/>
@@ -6025,37 +6035,35 @@
       <c r="O140" t="inlineStr"/>
       <c r="P140" t="inlineStr"/>
       <c r="Q140" t="inlineStr"/>
-      <c r="R140" t="n">
-        <v>3</v>
-      </c>
+      <c r="R140" t="inlineStr"/>
     </row>
     <row r="141">
       <c r="A141" t="inlineStr"/>
       <c r="B141" t="inlineStr">
         <is>
-          <t>Vital Signs</t>
+          <t>Patient Demographics/Information</t>
         </is>
       </c>
       <c r="C141" t="inlineStr">
         <is>
-          <t>US Core Blood Pressure Profile</t>
+          <t>US Core Patient Profile</t>
         </is>
       </c>
       <c r="D141" t="inlineStr">
         <is>
-          <t>Diastolic blood pressure</t>
+          <t>Phone Number Type</t>
         </is>
       </c>
       <c r="E141" t="inlineStr">
         <is>
-          <t>Observation</t>
+          <t>Patient</t>
         </is>
       </c>
       <c r="F141" t="inlineStr"/>
       <c r="G141" t="inlineStr"/>
       <c r="H141" t="inlineStr">
         <is>
-          <t>Observation</t>
+          <t>Patient.telecom.use</t>
         </is>
       </c>
       <c r="I141" t="inlineStr"/>
@@ -6073,29 +6081,29 @@
       <c r="A142" t="inlineStr"/>
       <c r="B142" t="inlineStr">
         <is>
-          <t>Vital Signs</t>
+          <t>Patient Demographics/Information</t>
         </is>
       </c>
       <c r="C142" t="inlineStr">
         <is>
-          <t>US Core Blood Pressure Profile</t>
+          <t>US Core RelatedPerson Profile</t>
         </is>
       </c>
       <c r="D142" t="inlineStr">
         <is>
-          <t>Systolic blood pressure</t>
+          <t>Related Person's Name</t>
         </is>
       </c>
       <c r="E142" t="inlineStr">
         <is>
-          <t>Observation</t>
+          <t>RelatedPerson</t>
         </is>
       </c>
       <c r="F142" t="inlineStr"/>
       <c r="G142" t="inlineStr"/>
       <c r="H142" t="inlineStr">
         <is>
-          <t>Observation</t>
+          <t>RelatedPerson.name</t>
         </is>
       </c>
       <c r="I142" t="inlineStr"/>
@@ -6113,29 +6121,29 @@
       <c r="A143" t="inlineStr"/>
       <c r="B143" t="inlineStr">
         <is>
-          <t>Vital Signs</t>
+          <t>Patient Demographics/Information</t>
         </is>
       </c>
       <c r="C143" t="inlineStr">
         <is>
-          <t>US Core Body Height Profile</t>
+          <t>US Core RelatedPerson Profile</t>
         </is>
       </c>
       <c r="D143" t="inlineStr">
         <is>
-          <t>Body height</t>
+          <t>Relationship Type</t>
         </is>
       </c>
       <c r="E143" t="inlineStr">
         <is>
-          <t>Observation</t>
+          <t>RelatedPerson</t>
         </is>
       </c>
       <c r="F143" t="inlineStr"/>
       <c r="G143" t="inlineStr"/>
       <c r="H143" t="inlineStr">
         <is>
-          <t>Observation</t>
+          <t>RelatedPerson.relationship</t>
         </is>
       </c>
       <c r="I143" t="inlineStr"/>
@@ -6153,17 +6161,17 @@
       <c r="A144" t="inlineStr"/>
       <c r="B144" t="inlineStr">
         <is>
-          <t>Vital Signs</t>
+          <t>Patient Demographics/Information</t>
         </is>
       </c>
       <c r="C144" t="inlineStr">
         <is>
-          <t>US Core Body Weight Profile</t>
+          <t>US Core Observation Occupation Profile</t>
         </is>
       </c>
       <c r="D144" t="inlineStr">
         <is>
-          <t>Body weight</t>
+          <t>Occupation</t>
         </is>
       </c>
       <c r="E144" t="inlineStr">
@@ -6193,17 +6201,17 @@
       <c r="A145" t="inlineStr"/>
       <c r="B145" t="inlineStr">
         <is>
-          <t>Vital Signs</t>
+          <t>Patient Demographics/Information</t>
         </is>
       </c>
       <c r="C145" t="inlineStr">
         <is>
-          <t>US Core Heart Rate Profile</t>
+          <t>US Core Observation Occupation Profile</t>
         </is>
       </c>
       <c r="D145" t="inlineStr">
         <is>
-          <t>Heart rate</t>
+          <t>Occupation Industry</t>
         </is>
       </c>
       <c r="E145" t="inlineStr">
@@ -6233,29 +6241,29 @@
       <c r="A146" t="inlineStr"/>
       <c r="B146" t="inlineStr">
         <is>
-          <t>Vital Signs</t>
+          <t>Patient Demographics/Information</t>
         </is>
       </c>
       <c r="C146" t="inlineStr">
         <is>
-          <t>US Core Respiratory Rate Profile</t>
+          <t>US Core Patient Profile</t>
         </is>
       </c>
       <c r="D146" t="inlineStr">
         <is>
-          <t>Respiratory rate</t>
+          <t>Patient Identifier</t>
         </is>
       </c>
       <c r="E146" t="inlineStr">
         <is>
-          <t>Observation</t>
+          <t>Patient</t>
         </is>
       </c>
       <c r="F146" t="inlineStr"/>
       <c r="G146" t="inlineStr"/>
       <c r="H146" t="inlineStr">
         <is>
-          <t>Observation</t>
+          <t>Patient.identifier</t>
         </is>
       </c>
       <c r="I146" t="inlineStr"/>
@@ -6273,29 +6281,29 @@
       <c r="A147" t="inlineStr"/>
       <c r="B147" t="inlineStr">
         <is>
-          <t>Vital Signs</t>
+          <t>Patient Demographics/Information</t>
         </is>
       </c>
       <c r="C147" t="inlineStr">
         <is>
-          <t>US Core Body Temperature Profile</t>
+          <t>US Core Patient Profile</t>
         </is>
       </c>
       <c r="D147" t="inlineStr">
         <is>
-          <t>Body temperature</t>
+          <t>Deceased Indicator</t>
         </is>
       </c>
       <c r="E147" t="inlineStr">
         <is>
-          <t>Observation</t>
+          <t>Patient</t>
         </is>
       </c>
       <c r="F147" t="inlineStr"/>
       <c r="G147" t="inlineStr"/>
       <c r="H147" t="inlineStr">
         <is>
-          <t>Observation</t>
+          <t>Patient.deceased[x]</t>
         </is>
       </c>
       <c r="I147" t="inlineStr"/>
@@ -6310,32 +6318,30 @@
       <c r="R147" t="inlineStr"/>
     </row>
     <row r="148">
-      <c r="A148" t="inlineStr"/>
+      <c r="A148" t="n">
+        <v>20</v>
+      </c>
       <c r="B148" t="inlineStr">
         <is>
-          <t>Vital Signs</t>
+          <t>Problems</t>
         </is>
       </c>
       <c r="C148" t="inlineStr">
         <is>
-          <t>US Core Pulse Oximetry Profile</t>
-        </is>
-      </c>
-      <c r="D148" t="inlineStr">
-        <is>
-          <t>Pulse oximetry</t>
-        </is>
-      </c>
+          <t>US Core Condition Problems and Health Concerns Profile</t>
+        </is>
+      </c>
+      <c r="D148" t="inlineStr"/>
       <c r="E148" t="inlineStr">
         <is>
-          <t>Observation</t>
+          <t>Condition</t>
         </is>
       </c>
       <c r="F148" t="inlineStr"/>
       <c r="G148" t="inlineStr"/>
       <c r="H148" t="inlineStr">
         <is>
-          <t>Observation</t>
+          <t>Condition</t>
         </is>
       </c>
       <c r="I148" t="inlineStr"/>
@@ -6353,33 +6359,41 @@
       <c r="A149" t="inlineStr"/>
       <c r="B149" t="inlineStr">
         <is>
-          <t>Vital Signs</t>
+          <t>Problems</t>
         </is>
       </c>
       <c r="C149" t="inlineStr">
         <is>
-          <t>US Core Pulse Oximetry Profile</t>
+          <t>US Core Condition Problems and Health Concerns Profile</t>
         </is>
       </c>
       <c r="D149" t="inlineStr">
         <is>
-          <t>Inhaled oxygen concentration</t>
+          <t>Problem</t>
         </is>
       </c>
       <c r="E149" t="inlineStr">
         <is>
-          <t>Observation</t>
+          <t>Condition</t>
         </is>
       </c>
       <c r="F149" t="inlineStr"/>
       <c r="G149" t="inlineStr"/>
       <c r="H149" t="inlineStr">
         <is>
-          <t>Observation</t>
-        </is>
-      </c>
-      <c r="I149" t="inlineStr"/>
-      <c r="J149" t="inlineStr"/>
+          <t>Condition.code</t>
+        </is>
+      </c>
+      <c r="I149" t="inlineStr">
+        <is>
+          <t>See Screening and Assessments Guidance</t>
+        </is>
+      </c>
+      <c r="J149" t="inlineStr">
+        <is>
+          <t>screening-and-assessments.html</t>
+        </is>
+      </c>
       <c r="K149" t="inlineStr"/>
       <c r="L149" t="inlineStr"/>
       <c r="M149" t="inlineStr"/>
@@ -6393,29 +6407,29 @@
       <c r="A150" t="inlineStr"/>
       <c r="B150" t="inlineStr">
         <is>
-          <t>Vital Signs</t>
+          <t>Problems</t>
         </is>
       </c>
       <c r="C150" t="inlineStr">
         <is>
-          <t>US Core Pediatric BMI for Age Observation Profile</t>
+          <t>US Core Condition Problems and Health Concerns Profile</t>
         </is>
       </c>
       <c r="D150" t="inlineStr">
         <is>
-          <t>BMI Percentile (2-20 years old)</t>
+          <t>Date of Resolution</t>
         </is>
       </c>
       <c r="E150" t="inlineStr">
         <is>
-          <t>Observation</t>
+          <t>Condition</t>
         </is>
       </c>
       <c r="F150" t="inlineStr"/>
       <c r="G150" t="inlineStr"/>
       <c r="H150" t="inlineStr">
         <is>
-          <t>Observation</t>
+          <t>Condition.abatement[x]</t>
         </is>
       </c>
       <c r="I150" t="inlineStr"/>
@@ -6433,29 +6447,37 @@
       <c r="A151" t="inlineStr"/>
       <c r="B151" t="inlineStr">
         <is>
-          <t>Vital Signs</t>
+          <t>Problems</t>
         </is>
       </c>
       <c r="C151" t="inlineStr">
         <is>
-          <t>US Core Pediatric Weight for Height Observation Profile</t>
+          <t>US Core Condition Problems and Health Concerns Profile |assertedDate Extension</t>
         </is>
       </c>
       <c r="D151" t="inlineStr">
         <is>
-          <t>Weight-for-length Percentile (Birth - 36 months)</t>
+          <t>Date of Diagnosis</t>
         </is>
       </c>
       <c r="E151" t="inlineStr">
         <is>
-          <t>Observation</t>
-        </is>
-      </c>
-      <c r="F151" t="inlineStr"/>
-      <c r="G151" t="inlineStr"/>
+          <t>Condition</t>
+        </is>
+      </c>
+      <c r="F151" t="inlineStr">
+        <is>
+          <t>assertedDate Extension</t>
+        </is>
+      </c>
+      <c r="G151" t="inlineStr">
+        <is>
+          <t>StructureDefinition-condition-assertedDate.html</t>
+        </is>
+      </c>
       <c r="H151" t="inlineStr">
         <is>
-          <t>Observation</t>
+          <t>Condition.extension.where(url='http://hl7.org/fhir/StructureDefinition/condition-assertedDate') | Condition.onset[x] | Condition.onsetDate</t>
         </is>
       </c>
       <c r="I151" t="inlineStr"/>
@@ -6473,29 +6495,29 @@
       <c r="A152" t="inlineStr"/>
       <c r="B152" t="inlineStr">
         <is>
-          <t>Vital Signs</t>
+          <t>Problems</t>
         </is>
       </c>
       <c r="C152" t="inlineStr">
         <is>
-          <t>US Core Pediatric Head Occipital Frontal Circumference Percentile Profile</t>
+          <t>US Core Condition Problems and Health Concerns Profile</t>
         </is>
       </c>
       <c r="D152" t="inlineStr">
         <is>
-          <t>Occipital Frontal Head Circumference Percentile (Birth - 36 months)</t>
+          <t>Date of Onset</t>
         </is>
       </c>
       <c r="E152" t="inlineStr">
         <is>
-          <t>Observation</t>
+          <t>Condition</t>
         </is>
       </c>
       <c r="F152" t="inlineStr"/>
       <c r="G152" t="inlineStr"/>
       <c r="H152" t="inlineStr">
         <is>
-          <t>Observation</t>
+          <t>Condition.onset[x]</t>
         </is>
       </c>
       <c r="I152" t="inlineStr"/>
@@ -6509,6 +6531,990 @@
       <c r="Q152" t="inlineStr"/>
       <c r="R152" t="inlineStr"/>
     </row>
+    <row r="153">
+      <c r="A153" t="inlineStr"/>
+      <c r="B153" t="inlineStr">
+        <is>
+          <t>Problems</t>
+        </is>
+      </c>
+      <c r="C153" t="inlineStr">
+        <is>
+          <t>US Core Condition Problems and Health Concerns Profile</t>
+        </is>
+      </c>
+      <c r="D153" t="inlineStr">
+        <is>
+          <t>Health Concern</t>
+        </is>
+      </c>
+      <c r="E153" t="inlineStr">
+        <is>
+          <t>Condition</t>
+        </is>
+      </c>
+      <c r="F153" t="inlineStr"/>
+      <c r="G153" t="inlineStr"/>
+      <c r="H153" t="inlineStr">
+        <is>
+          <t>Condition</t>
+        </is>
+      </c>
+      <c r="I153" t="inlineStr">
+        <is>
+          <t>See Screening and Assessments Guidance</t>
+        </is>
+      </c>
+      <c r="J153" t="inlineStr">
+        <is>
+          <t>screening-and-assessments.html</t>
+        </is>
+      </c>
+      <c r="K153" t="inlineStr"/>
+      <c r="L153" t="inlineStr"/>
+      <c r="M153" t="inlineStr"/>
+      <c r="N153" t="inlineStr"/>
+      <c r="O153" t="inlineStr"/>
+      <c r="P153" t="inlineStr"/>
+      <c r="Q153" t="inlineStr"/>
+      <c r="R153" t="inlineStr"/>
+    </row>
+    <row r="154">
+      <c r="A154" t="inlineStr"/>
+      <c r="B154" t="inlineStr">
+        <is>
+          <t>Problems</t>
+        </is>
+      </c>
+      <c r="C154" t="inlineStr">
+        <is>
+          <t>US Core Condition Problems and Health Concerns Profile</t>
+        </is>
+      </c>
+      <c r="D154" t="inlineStr">
+        <is>
+          <t>Condition Status</t>
+        </is>
+      </c>
+      <c r="E154" t="inlineStr">
+        <is>
+          <t>Condition</t>
+        </is>
+      </c>
+      <c r="F154" t="inlineStr"/>
+      <c r="G154" t="inlineStr"/>
+      <c r="H154" t="inlineStr">
+        <is>
+          <t>Condition.clinicalStatus</t>
+        </is>
+      </c>
+      <c r="I154" t="inlineStr"/>
+      <c r="J154" t="inlineStr"/>
+      <c r="K154" t="inlineStr"/>
+      <c r="L154" t="inlineStr"/>
+      <c r="M154" t="inlineStr"/>
+      <c r="N154" t="inlineStr"/>
+      <c r="O154" t="inlineStr"/>
+      <c r="P154" t="inlineStr"/>
+      <c r="Q154" t="inlineStr"/>
+      <c r="R154" t="inlineStr"/>
+    </row>
+    <row r="155">
+      <c r="A155" t="n">
+        <v>21</v>
+      </c>
+      <c r="B155" t="inlineStr">
+        <is>
+          <t>Procedures</t>
+        </is>
+      </c>
+      <c r="C155" t="inlineStr">
+        <is>
+          <t>US Core Procedure Profile | US Core ServiceRequest Profile</t>
+        </is>
+      </c>
+      <c r="D155" t="inlineStr"/>
+      <c r="E155" t="inlineStr"/>
+      <c r="F155" t="inlineStr"/>
+      <c r="G155" t="inlineStr"/>
+      <c r="H155" t="inlineStr">
+        <is>
+          <t>Procedure | ServiceRequest</t>
+        </is>
+      </c>
+      <c r="I155" t="inlineStr"/>
+      <c r="J155" t="inlineStr"/>
+      <c r="K155" t="inlineStr"/>
+      <c r="L155" t="inlineStr"/>
+      <c r="M155" t="inlineStr"/>
+      <c r="N155" t="inlineStr"/>
+      <c r="O155" t="inlineStr"/>
+      <c r="P155" t="inlineStr"/>
+      <c r="Q155" t="inlineStr"/>
+      <c r="R155" t="inlineStr"/>
+    </row>
+    <row r="156">
+      <c r="A156" t="inlineStr"/>
+      <c r="B156" t="inlineStr">
+        <is>
+          <t>Procedures</t>
+        </is>
+      </c>
+      <c r="C156" t="inlineStr">
+        <is>
+          <t>US Core Procedure Profile | US Core ServiceRequest Profile</t>
+        </is>
+      </c>
+      <c r="D156" t="inlineStr">
+        <is>
+          <t>Procedure</t>
+        </is>
+      </c>
+      <c r="E156" t="inlineStr">
+        <is>
+          <t>Procedure | ServiceRequest</t>
+        </is>
+      </c>
+      <c r="F156" t="inlineStr"/>
+      <c r="G156" t="inlineStr"/>
+      <c r="H156" t="inlineStr">
+        <is>
+          <t>Procedure | ServiceRequest</t>
+        </is>
+      </c>
+      <c r="I156" t="inlineStr">
+        <is>
+          <t>See Screening and Assessments Guidance</t>
+        </is>
+      </c>
+      <c r="J156" t="inlineStr">
+        <is>
+          <t>screening-and-assessments.html</t>
+        </is>
+      </c>
+      <c r="K156" t="inlineStr"/>
+      <c r="L156" t="inlineStr"/>
+      <c r="M156" t="inlineStr"/>
+      <c r="N156" t="inlineStr"/>
+      <c r="O156" t="inlineStr"/>
+      <c r="P156" t="inlineStr"/>
+      <c r="Q156" t="inlineStr"/>
+      <c r="R156" t="inlineStr"/>
+    </row>
+    <row r="157">
+      <c r="A157" t="inlineStr"/>
+      <c r="B157" t="inlineStr">
+        <is>
+          <t>Procedures</t>
+        </is>
+      </c>
+      <c r="C157" t="inlineStr">
+        <is>
+          <t>US Core ServiceRequest Profile | US Core Procedure Profile</t>
+        </is>
+      </c>
+      <c r="D157" t="inlineStr">
+        <is>
+          <t>Reason for Referral</t>
+        </is>
+      </c>
+      <c r="E157" t="inlineStr">
+        <is>
+          <t>ServiceRequest | Procedure</t>
+        </is>
+      </c>
+      <c r="F157" t="inlineStr"/>
+      <c r="G157" t="inlineStr"/>
+      <c r="H157" t="inlineStr">
+        <is>
+          <t>ServiceRequest.reasonCode | ServiceRequest.reasonReference | Procedure.reasonCode | Procedure.reasonReference</t>
+        </is>
+      </c>
+      <c r="I157" t="inlineStr"/>
+      <c r="J157" t="inlineStr"/>
+      <c r="K157" t="inlineStr"/>
+      <c r="L157" t="inlineStr"/>
+      <c r="M157" t="inlineStr"/>
+      <c r="N157" t="inlineStr"/>
+      <c r="O157" t="inlineStr"/>
+      <c r="P157" t="inlineStr"/>
+      <c r="Q157" t="inlineStr"/>
+      <c r="R157" t="inlineStr"/>
+    </row>
+    <row r="158">
+      <c r="A158" t="inlineStr"/>
+      <c r="B158" t="inlineStr">
+        <is>
+          <t>Procedures</t>
+        </is>
+      </c>
+      <c r="C158" t="inlineStr">
+        <is>
+          <t>US Core Procedure Profile</t>
+        </is>
+      </c>
+      <c r="D158" t="inlineStr">
+        <is>
+          <t>Procedure Status</t>
+        </is>
+      </c>
+      <c r="E158" t="inlineStr">
+        <is>
+          <t>Procedure</t>
+        </is>
+      </c>
+      <c r="F158" t="inlineStr"/>
+      <c r="G158" t="inlineStr"/>
+      <c r="H158" t="inlineStr">
+        <is>
+          <t>Procedure.status</t>
+        </is>
+      </c>
+      <c r="I158" t="inlineStr"/>
+      <c r="J158" t="inlineStr"/>
+      <c r="K158" t="inlineStr"/>
+      <c r="L158" t="inlineStr"/>
+      <c r="M158" t="inlineStr"/>
+      <c r="N158" t="inlineStr"/>
+      <c r="O158" t="inlineStr"/>
+      <c r="P158" t="inlineStr"/>
+      <c r="Q158" t="inlineStr"/>
+      <c r="R158" t="inlineStr"/>
+    </row>
+    <row r="159">
+      <c r="A159" t="n">
+        <v>22</v>
+      </c>
+      <c r="B159" t="inlineStr">
+        <is>
+          <t>Provenance</t>
+        </is>
+      </c>
+      <c r="C159" t="inlineStr">
+        <is>
+          <t>US Core Provenance Profile</t>
+        </is>
+      </c>
+      <c r="D159" t="inlineStr"/>
+      <c r="E159" t="inlineStr"/>
+      <c r="F159" t="inlineStr"/>
+      <c r="G159" t="inlineStr"/>
+      <c r="H159" t="inlineStr">
+        <is>
+          <t>Provenance</t>
+        </is>
+      </c>
+      <c r="I159" t="inlineStr">
+        <is>
+          <t>See Basic Provenance Guidance</t>
+        </is>
+      </c>
+      <c r="J159" t="inlineStr">
+        <is>
+          <t>basic-provenance.html</t>
+        </is>
+      </c>
+      <c r="K159" t="inlineStr"/>
+      <c r="L159" t="inlineStr"/>
+      <c r="M159" t="inlineStr"/>
+      <c r="N159" t="inlineStr"/>
+      <c r="O159" t="inlineStr"/>
+      <c r="P159" t="inlineStr"/>
+      <c r="Q159" t="inlineStr"/>
+      <c r="R159" t="inlineStr"/>
+    </row>
+    <row r="160">
+      <c r="A160" t="inlineStr"/>
+      <c r="B160" t="inlineStr">
+        <is>
+          <t>Provenance</t>
+        </is>
+      </c>
+      <c r="C160" t="inlineStr"/>
+      <c r="D160" t="inlineStr">
+        <is>
+          <t>Author</t>
+        </is>
+      </c>
+      <c r="E160" t="inlineStr"/>
+      <c r="F160" t="inlineStr"/>
+      <c r="G160" t="inlineStr"/>
+      <c r="H160" t="inlineStr">
+        <is>
+          <t>Provenance.recorded</t>
+        </is>
+      </c>
+      <c r="I160" t="inlineStr"/>
+      <c r="J160" t="inlineStr"/>
+      <c r="K160" t="inlineStr"/>
+      <c r="L160" t="inlineStr"/>
+      <c r="M160" t="inlineStr"/>
+      <c r="N160" t="inlineStr"/>
+      <c r="O160" t="inlineStr"/>
+      <c r="P160" t="inlineStr"/>
+      <c r="Q160" t="inlineStr"/>
+      <c r="R160" t="inlineStr"/>
+    </row>
+    <row r="161">
+      <c r="A161" t="inlineStr"/>
+      <c r="B161" t="inlineStr">
+        <is>
+          <t>Provenance</t>
+        </is>
+      </c>
+      <c r="C161" t="inlineStr"/>
+      <c r="D161" t="inlineStr">
+        <is>
+          <t>Author Role</t>
+        </is>
+      </c>
+      <c r="E161" t="inlineStr"/>
+      <c r="F161" t="inlineStr"/>
+      <c r="G161" t="inlineStr"/>
+      <c r="H161" t="inlineStr">
+        <is>
+          <t>Provenance.agent</t>
+        </is>
+      </c>
+      <c r="I161" t="inlineStr"/>
+      <c r="J161" t="inlineStr"/>
+      <c r="K161" t="inlineStr"/>
+      <c r="L161" t="inlineStr"/>
+      <c r="M161" t="inlineStr"/>
+      <c r="N161" t="inlineStr"/>
+      <c r="O161" t="inlineStr"/>
+      <c r="P161" t="inlineStr"/>
+      <c r="Q161" t="inlineStr"/>
+      <c r="R161" t="inlineStr"/>
+    </row>
+    <row r="162">
+      <c r="A162" t="inlineStr"/>
+      <c r="B162" t="inlineStr">
+        <is>
+          <t>Provenance</t>
+        </is>
+      </c>
+      <c r="C162" t="inlineStr">
+        <is>
+          <t>US Core Provenance Profile</t>
+        </is>
+      </c>
+      <c r="D162" t="inlineStr">
+        <is>
+          <t>Author Time Stamp</t>
+        </is>
+      </c>
+      <c r="E162" t="inlineStr"/>
+      <c r="F162" t="inlineStr"/>
+      <c r="G162" t="inlineStr"/>
+      <c r="H162" t="inlineStr">
+        <is>
+          <t>Provenance.recorded</t>
+        </is>
+      </c>
+      <c r="I162" t="inlineStr"/>
+      <c r="J162" t="inlineStr"/>
+      <c r="K162" t="inlineStr"/>
+      <c r="L162" t="inlineStr"/>
+      <c r="M162" t="inlineStr"/>
+      <c r="N162" t="inlineStr"/>
+      <c r="O162" t="inlineStr"/>
+      <c r="P162" t="inlineStr"/>
+      <c r="Q162" t="inlineStr"/>
+      <c r="R162" t="inlineStr"/>
+    </row>
+    <row r="163">
+      <c r="A163" t="inlineStr"/>
+      <c r="B163" t="inlineStr">
+        <is>
+          <t>Provenance</t>
+        </is>
+      </c>
+      <c r="C163" t="inlineStr">
+        <is>
+          <t>US Core Provenance Profile</t>
+        </is>
+      </c>
+      <c r="D163" t="inlineStr">
+        <is>
+          <t>Author Organization</t>
+        </is>
+      </c>
+      <c r="E163" t="inlineStr"/>
+      <c r="F163" t="inlineStr"/>
+      <c r="G163" t="inlineStr"/>
+      <c r="H163" t="inlineStr">
+        <is>
+          <t>Provenance.agent</t>
+        </is>
+      </c>
+      <c r="I163" t="inlineStr"/>
+      <c r="J163" t="inlineStr"/>
+      <c r="K163" t="inlineStr"/>
+      <c r="L163" t="inlineStr"/>
+      <c r="M163" t="inlineStr"/>
+      <c r="N163" t="inlineStr"/>
+      <c r="O163" t="inlineStr"/>
+      <c r="P163" t="inlineStr"/>
+      <c r="Q163" t="inlineStr"/>
+      <c r="R163" t="inlineStr"/>
+    </row>
+    <row r="164">
+      <c r="A164" t="n">
+        <v>23</v>
+      </c>
+      <c r="B164" t="inlineStr">
+        <is>
+          <t>Vital Signs</t>
+        </is>
+      </c>
+      <c r="C164" t="inlineStr">
+        <is>
+          <t>US Core Vital Signs Profile</t>
+        </is>
+      </c>
+      <c r="D164" t="inlineStr"/>
+      <c r="E164" t="inlineStr"/>
+      <c r="F164" t="inlineStr"/>
+      <c r="G164" t="inlineStr"/>
+      <c r="H164" t="inlineStr">
+        <is>
+          <t>Observation</t>
+        </is>
+      </c>
+      <c r="I164" t="inlineStr"/>
+      <c r="J164" t="inlineStr"/>
+      <c r="K164" t="inlineStr"/>
+      <c r="L164" t="inlineStr"/>
+      <c r="M164" t="inlineStr"/>
+      <c r="N164" t="inlineStr"/>
+      <c r="O164" t="inlineStr"/>
+      <c r="P164" t="inlineStr"/>
+      <c r="Q164" t="inlineStr"/>
+      <c r="R164" t="inlineStr"/>
+    </row>
+    <row r="165">
+      <c r="A165" t="inlineStr"/>
+      <c r="B165" t="inlineStr">
+        <is>
+          <t>Vital Signs</t>
+        </is>
+      </c>
+      <c r="C165" t="inlineStr">
+        <is>
+          <t>US Core Average Blood Pressure Profile</t>
+        </is>
+      </c>
+      <c r="D165" t="inlineStr">
+        <is>
+          <t>Average Blood Pressure</t>
+        </is>
+      </c>
+      <c r="E165" t="inlineStr">
+        <is>
+          <t>Observation</t>
+        </is>
+      </c>
+      <c r="F165" t="inlineStr"/>
+      <c r="G165" t="inlineStr"/>
+      <c r="H165" t="inlineStr">
+        <is>
+          <t>Observation</t>
+        </is>
+      </c>
+      <c r="I165" t="inlineStr"/>
+      <c r="J165" t="inlineStr"/>
+      <c r="K165" t="inlineStr"/>
+      <c r="L165" t="inlineStr"/>
+      <c r="M165" t="inlineStr"/>
+      <c r="N165" t="inlineStr"/>
+      <c r="O165" t="inlineStr"/>
+      <c r="P165" t="inlineStr"/>
+      <c r="Q165" t="inlineStr"/>
+      <c r="R165" t="n">
+        <v>3</v>
+      </c>
+    </row>
+    <row r="166">
+      <c r="A166" t="inlineStr"/>
+      <c r="B166" t="inlineStr">
+        <is>
+          <t>Vital Signs</t>
+        </is>
+      </c>
+      <c r="C166" t="inlineStr">
+        <is>
+          <t>US Core Blood Pressure Profile</t>
+        </is>
+      </c>
+      <c r="D166" t="inlineStr">
+        <is>
+          <t>Diastolic Blood Pressure</t>
+        </is>
+      </c>
+      <c r="E166" t="inlineStr">
+        <is>
+          <t>Observation</t>
+        </is>
+      </c>
+      <c r="F166" t="inlineStr"/>
+      <c r="G166" t="inlineStr"/>
+      <c r="H166" t="inlineStr">
+        <is>
+          <t>Observation</t>
+        </is>
+      </c>
+      <c r="I166" t="inlineStr"/>
+      <c r="J166" t="inlineStr"/>
+      <c r="K166" t="inlineStr"/>
+      <c r="L166" t="inlineStr"/>
+      <c r="M166" t="inlineStr"/>
+      <c r="N166" t="inlineStr"/>
+      <c r="O166" t="inlineStr"/>
+      <c r="P166" t="inlineStr"/>
+      <c r="Q166" t="inlineStr"/>
+      <c r="R166" t="inlineStr"/>
+    </row>
+    <row r="167">
+      <c r="A167" t="inlineStr"/>
+      <c r="B167" t="inlineStr">
+        <is>
+          <t>Vital Signs</t>
+        </is>
+      </c>
+      <c r="C167" t="inlineStr">
+        <is>
+          <t>US Core Blood Pressure Profile</t>
+        </is>
+      </c>
+      <c r="D167" t="inlineStr">
+        <is>
+          <t>Systolic Blood Pressure</t>
+        </is>
+      </c>
+      <c r="E167" t="inlineStr">
+        <is>
+          <t>Observation</t>
+        </is>
+      </c>
+      <c r="F167" t="inlineStr"/>
+      <c r="G167" t="inlineStr"/>
+      <c r="H167" t="inlineStr">
+        <is>
+          <t>Observation</t>
+        </is>
+      </c>
+      <c r="I167" t="inlineStr"/>
+      <c r="J167" t="inlineStr"/>
+      <c r="K167" t="inlineStr"/>
+      <c r="L167" t="inlineStr"/>
+      <c r="M167" t="inlineStr"/>
+      <c r="N167" t="inlineStr"/>
+      <c r="O167" t="inlineStr"/>
+      <c r="P167" t="inlineStr"/>
+      <c r="Q167" t="inlineStr"/>
+      <c r="R167" t="inlineStr"/>
+    </row>
+    <row r="168">
+      <c r="A168" t="inlineStr"/>
+      <c r="B168" t="inlineStr">
+        <is>
+          <t>Vital Signs</t>
+        </is>
+      </c>
+      <c r="C168" t="inlineStr">
+        <is>
+          <t>US Core Body Height Profile</t>
+        </is>
+      </c>
+      <c r="D168" t="inlineStr">
+        <is>
+          <t>Body Height</t>
+        </is>
+      </c>
+      <c r="E168" t="inlineStr">
+        <is>
+          <t>Observation</t>
+        </is>
+      </c>
+      <c r="F168" t="inlineStr"/>
+      <c r="G168" t="inlineStr"/>
+      <c r="H168" t="inlineStr">
+        <is>
+          <t>Observation</t>
+        </is>
+      </c>
+      <c r="I168" t="inlineStr"/>
+      <c r="J168" t="inlineStr"/>
+      <c r="K168" t="inlineStr"/>
+      <c r="L168" t="inlineStr"/>
+      <c r="M168" t="inlineStr"/>
+      <c r="N168" t="inlineStr"/>
+      <c r="O168" t="inlineStr"/>
+      <c r="P168" t="inlineStr"/>
+      <c r="Q168" t="inlineStr"/>
+      <c r="R168" t="inlineStr"/>
+    </row>
+    <row r="169">
+      <c r="A169" t="inlineStr"/>
+      <c r="B169" t="inlineStr">
+        <is>
+          <t>Vital Signs</t>
+        </is>
+      </c>
+      <c r="C169" t="inlineStr">
+        <is>
+          <t>US Core Body Weight Profile</t>
+        </is>
+      </c>
+      <c r="D169" t="inlineStr">
+        <is>
+          <t>Body Weight</t>
+        </is>
+      </c>
+      <c r="E169" t="inlineStr">
+        <is>
+          <t>Observation</t>
+        </is>
+      </c>
+      <c r="F169" t="inlineStr"/>
+      <c r="G169" t="inlineStr"/>
+      <c r="H169" t="inlineStr">
+        <is>
+          <t>Observation</t>
+        </is>
+      </c>
+      <c r="I169" t="inlineStr"/>
+      <c r="J169" t="inlineStr"/>
+      <c r="K169" t="inlineStr"/>
+      <c r="L169" t="inlineStr"/>
+      <c r="M169" t="inlineStr"/>
+      <c r="N169" t="inlineStr"/>
+      <c r="O169" t="inlineStr"/>
+      <c r="P169" t="inlineStr"/>
+      <c r="Q169" t="inlineStr"/>
+      <c r="R169" t="inlineStr"/>
+    </row>
+    <row r="170">
+      <c r="A170" t="inlineStr"/>
+      <c r="B170" t="inlineStr">
+        <is>
+          <t>Vital Signs</t>
+        </is>
+      </c>
+      <c r="C170" t="inlineStr">
+        <is>
+          <t>US Core Heart Rate Profile</t>
+        </is>
+      </c>
+      <c r="D170" t="inlineStr">
+        <is>
+          <t>Heart Rate</t>
+        </is>
+      </c>
+      <c r="E170" t="inlineStr">
+        <is>
+          <t>Observation</t>
+        </is>
+      </c>
+      <c r="F170" t="inlineStr"/>
+      <c r="G170" t="inlineStr"/>
+      <c r="H170" t="inlineStr">
+        <is>
+          <t>Observation</t>
+        </is>
+      </c>
+      <c r="I170" t="inlineStr"/>
+      <c r="J170" t="inlineStr"/>
+      <c r="K170" t="inlineStr"/>
+      <c r="L170" t="inlineStr"/>
+      <c r="M170" t="inlineStr"/>
+      <c r="N170" t="inlineStr"/>
+      <c r="O170" t="inlineStr"/>
+      <c r="P170" t="inlineStr"/>
+      <c r="Q170" t="inlineStr"/>
+      <c r="R170" t="inlineStr"/>
+    </row>
+    <row r="171">
+      <c r="A171" t="inlineStr"/>
+      <c r="B171" t="inlineStr">
+        <is>
+          <t>Vital Signs</t>
+        </is>
+      </c>
+      <c r="C171" t="inlineStr">
+        <is>
+          <t>US Core Respiratory Rate Profile</t>
+        </is>
+      </c>
+      <c r="D171" t="inlineStr">
+        <is>
+          <t>Respiratory Rate</t>
+        </is>
+      </c>
+      <c r="E171" t="inlineStr">
+        <is>
+          <t>Observation</t>
+        </is>
+      </c>
+      <c r="F171" t="inlineStr"/>
+      <c r="G171" t="inlineStr"/>
+      <c r="H171" t="inlineStr">
+        <is>
+          <t>Observation</t>
+        </is>
+      </c>
+      <c r="I171" t="inlineStr"/>
+      <c r="J171" t="inlineStr"/>
+      <c r="K171" t="inlineStr"/>
+      <c r="L171" t="inlineStr"/>
+      <c r="M171" t="inlineStr"/>
+      <c r="N171" t="inlineStr"/>
+      <c r="O171" t="inlineStr"/>
+      <c r="P171" t="inlineStr"/>
+      <c r="Q171" t="inlineStr"/>
+      <c r="R171" t="inlineStr"/>
+    </row>
+    <row r="172">
+      <c r="A172" t="inlineStr"/>
+      <c r="B172" t="inlineStr">
+        <is>
+          <t>Vital Signs</t>
+        </is>
+      </c>
+      <c r="C172" t="inlineStr">
+        <is>
+          <t>US Core Body Temperature Profile</t>
+        </is>
+      </c>
+      <c r="D172" t="inlineStr">
+        <is>
+          <t>Body Temperature</t>
+        </is>
+      </c>
+      <c r="E172" t="inlineStr">
+        <is>
+          <t>Observation</t>
+        </is>
+      </c>
+      <c r="F172" t="inlineStr"/>
+      <c r="G172" t="inlineStr"/>
+      <c r="H172" t="inlineStr">
+        <is>
+          <t>Observation</t>
+        </is>
+      </c>
+      <c r="I172" t="inlineStr"/>
+      <c r="J172" t="inlineStr"/>
+      <c r="K172" t="inlineStr"/>
+      <c r="L172" t="inlineStr"/>
+      <c r="M172" t="inlineStr"/>
+      <c r="N172" t="inlineStr"/>
+      <c r="O172" t="inlineStr"/>
+      <c r="P172" t="inlineStr"/>
+      <c r="Q172" t="inlineStr"/>
+      <c r="R172" t="inlineStr"/>
+    </row>
+    <row r="173">
+      <c r="A173" t="inlineStr"/>
+      <c r="B173" t="inlineStr">
+        <is>
+          <t>Vital Signs</t>
+        </is>
+      </c>
+      <c r="C173" t="inlineStr">
+        <is>
+          <t>US Core Pulse Oximetry Profile</t>
+        </is>
+      </c>
+      <c r="D173" t="inlineStr">
+        <is>
+          <t>Pulse Oximetry</t>
+        </is>
+      </c>
+      <c r="E173" t="inlineStr">
+        <is>
+          <t>Observation</t>
+        </is>
+      </c>
+      <c r="F173" t="inlineStr"/>
+      <c r="G173" t="inlineStr"/>
+      <c r="H173" t="inlineStr">
+        <is>
+          <t>Observation</t>
+        </is>
+      </c>
+      <c r="I173" t="inlineStr"/>
+      <c r="J173" t="inlineStr"/>
+      <c r="K173" t="inlineStr"/>
+      <c r="L173" t="inlineStr"/>
+      <c r="M173" t="inlineStr"/>
+      <c r="N173" t="inlineStr"/>
+      <c r="O173" t="inlineStr"/>
+      <c r="P173" t="inlineStr"/>
+      <c r="Q173" t="inlineStr"/>
+      <c r="R173" t="inlineStr"/>
+    </row>
+    <row r="174">
+      <c r="A174" t="inlineStr"/>
+      <c r="B174" t="inlineStr">
+        <is>
+          <t>Vital Signs</t>
+        </is>
+      </c>
+      <c r="C174" t="inlineStr">
+        <is>
+          <t>US Core Pulse Oximetry Profile</t>
+        </is>
+      </c>
+      <c r="D174" t="inlineStr">
+        <is>
+          <t>Inhaled Oxygen Concentration</t>
+        </is>
+      </c>
+      <c r="E174" t="inlineStr">
+        <is>
+          <t>Observation</t>
+        </is>
+      </c>
+      <c r="F174" t="inlineStr"/>
+      <c r="G174" t="inlineStr"/>
+      <c r="H174" t="inlineStr">
+        <is>
+          <t>Observation</t>
+        </is>
+      </c>
+      <c r="I174" t="inlineStr"/>
+      <c r="J174" t="inlineStr"/>
+      <c r="K174" t="inlineStr"/>
+      <c r="L174" t="inlineStr"/>
+      <c r="M174" t="inlineStr"/>
+      <c r="N174" t="inlineStr"/>
+      <c r="O174" t="inlineStr"/>
+      <c r="P174" t="inlineStr"/>
+      <c r="Q174" t="inlineStr"/>
+      <c r="R174" t="inlineStr"/>
+    </row>
+    <row r="175">
+      <c r="A175" t="inlineStr"/>
+      <c r="B175" t="inlineStr">
+        <is>
+          <t>Vital Signs</t>
+        </is>
+      </c>
+      <c r="C175" t="inlineStr">
+        <is>
+          <t>US Core Pediatric BMI for Age Observation Profile</t>
+        </is>
+      </c>
+      <c r="D175" t="inlineStr">
+        <is>
+          <t>BMI Percentile (2-20 years)</t>
+        </is>
+      </c>
+      <c r="E175" t="inlineStr">
+        <is>
+          <t>Observation</t>
+        </is>
+      </c>
+      <c r="F175" t="inlineStr"/>
+      <c r="G175" t="inlineStr"/>
+      <c r="H175" t="inlineStr">
+        <is>
+          <t>Observation</t>
+        </is>
+      </c>
+      <c r="I175" t="inlineStr"/>
+      <c r="J175" t="inlineStr"/>
+      <c r="K175" t="inlineStr"/>
+      <c r="L175" t="inlineStr"/>
+      <c r="M175" t="inlineStr"/>
+      <c r="N175" t="inlineStr"/>
+      <c r="O175" t="inlineStr"/>
+      <c r="P175" t="inlineStr"/>
+      <c r="Q175" t="inlineStr"/>
+      <c r="R175" t="inlineStr"/>
+    </row>
+    <row r="176">
+      <c r="A176" t="inlineStr"/>
+      <c r="B176" t="inlineStr">
+        <is>
+          <t>Vital Signs</t>
+        </is>
+      </c>
+      <c r="C176" t="inlineStr">
+        <is>
+          <t>US Core Pediatric Weight for Height Observation Profile</t>
+        </is>
+      </c>
+      <c r="D176" t="inlineStr">
+        <is>
+          <t>Weight-for-length Percentile (Birth - 24 Months)</t>
+        </is>
+      </c>
+      <c r="E176" t="inlineStr">
+        <is>
+          <t>Observation</t>
+        </is>
+      </c>
+      <c r="F176" t="inlineStr"/>
+      <c r="G176" t="inlineStr"/>
+      <c r="H176" t="inlineStr">
+        <is>
+          <t>Observation</t>
+        </is>
+      </c>
+      <c r="I176" t="inlineStr"/>
+      <c r="J176" t="inlineStr"/>
+      <c r="K176" t="inlineStr"/>
+      <c r="L176" t="inlineStr"/>
+      <c r="M176" t="inlineStr"/>
+      <c r="N176" t="inlineStr"/>
+      <c r="O176" t="inlineStr"/>
+      <c r="P176" t="inlineStr"/>
+      <c r="Q176" t="inlineStr"/>
+      <c r="R176" t="inlineStr"/>
+    </row>
+    <row r="177">
+      <c r="A177" t="inlineStr"/>
+      <c r="B177" t="inlineStr">
+        <is>
+          <t>Vital Signs</t>
+        </is>
+      </c>
+      <c r="C177" t="inlineStr">
+        <is>
+          <t>US Core Pediatric Head Occipital Frontal Circumference Percentile Profile</t>
+        </is>
+      </c>
+      <c r="D177" t="inlineStr">
+        <is>
+          <t>Head Occipital-frontal Circumference Percentile (Birth - 36 Months)</t>
+        </is>
+      </c>
+      <c r="E177" t="inlineStr">
+        <is>
+          <t>Observation</t>
+        </is>
+      </c>
+      <c r="F177" t="inlineStr"/>
+      <c r="G177" t="inlineStr"/>
+      <c r="H177" t="inlineStr">
+        <is>
+          <t>Observation</t>
+        </is>
+      </c>
+      <c r="I177" t="inlineStr"/>
+      <c r="J177" t="inlineStr"/>
+      <c r="K177" t="inlineStr"/>
+      <c r="L177" t="inlineStr"/>
+      <c r="M177" t="inlineStr"/>
+      <c r="N177" t="inlineStr"/>
+      <c r="O177" t="inlineStr"/>
+      <c r="P177" t="inlineStr"/>
+      <c r="Q177" t="inlineStr"/>
+      <c r="R177" t="inlineStr"/>
+    </row>
   </sheetData>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
 </worksheet>
